--- a/Excel/RobotConfig.xlsx
+++ b/Excel/RobotConfig.xlsx
@@ -1,39 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3432DD56-A32F-40F3-87D9-2AC3B1CAD8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="809"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RobotConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="I3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +48,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="1">
+    <comment ref="J3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -86,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1">
+    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -108,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -135,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="64">
   <si>
     <t>cs</t>
   </si>
@@ -332,14 +325,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,150 +367,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -534,8 +377,22 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -554,194 +411,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -762,360 +433,74 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 6" xfId="50"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1373,13 +758,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L85"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -1396,7 +781,7 @@
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1412,7 +797,7 @@
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1428,7 +813,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
@@ -1462,7 +847,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
@@ -1496,7 +881,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
@@ -1530,7 +915,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B6" s="7"/>
       <c r="C6" s="5">
         <v>1001</v>
@@ -1557,7 +942,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="9"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="7" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B7" s="7"/>
       <c r="C7" s="5">
         <v>2101</v>
@@ -1574,7 +959,7 @@
       <c r="G7" s="5">
         <v>101</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="12" t="s">
         <v>27</v>
       </c>
       <c r="I7" s="10">
@@ -1586,11 +971,11 @@
       <c r="K7" s="5">
         <v>110001</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="8" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B8" s="7"/>
       <c r="C8" s="5">
         <v>2102</v>
@@ -1607,7 +992,7 @@
       <c r="G8" s="5">
         <v>102</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="12" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="10">
@@ -1619,11 +1004,11 @@
       <c r="K8" s="5">
         <v>110001</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="9" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B9" s="7"/>
       <c r="C9" s="5">
         <v>2103</v>
@@ -1640,7 +1025,7 @@
       <c r="G9" s="5">
         <v>103</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="12" t="s">
         <v>29</v>
       </c>
       <c r="I9" s="10">
@@ -1652,11 +1037,11 @@
       <c r="K9" s="5">
         <v>110001</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="10" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B10" s="7"/>
       <c r="C10" s="5">
         <v>2104</v>
@@ -1673,7 +1058,7 @@
       <c r="G10" s="5">
         <v>201</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="10">
@@ -1685,11 +1070,11 @@
       <c r="K10" s="5">
         <v>110001</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="11" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B11" s="7"/>
       <c r="C11" s="5">
         <v>2105</v>
@@ -1706,7 +1091,7 @@
       <c r="G11" s="5">
         <v>202</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="10">
@@ -1718,11 +1103,11 @@
       <c r="K11" s="5">
         <v>110001</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="12" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B12" s="7"/>
       <c r="C12" s="5">
         <v>2106</v>
@@ -1739,7 +1124,7 @@
       <c r="G12" s="5">
         <v>203</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="10">
@@ -1751,11 +1136,11 @@
       <c r="K12" s="5">
         <v>110001</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="13" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B13" s="7"/>
       <c r="C13" s="5">
         <f>C7+100</f>
@@ -1773,7 +1158,7 @@
       <c r="G13" s="5">
         <v>101</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="12" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="10">
@@ -1785,14 +1170,14 @@
       <c r="K13" s="5">
         <v>110002</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="14" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B14" s="7"/>
       <c r="C14" s="5">
-        <f t="shared" ref="C14:C42" si="0">C8+100</f>
+        <f t="shared" ref="C14:C48" si="0">C8+100</f>
         <v>2202</v>
       </c>
       <c r="D14" s="5">
@@ -1807,7 +1192,7 @@
       <c r="G14" s="5">
         <v>102</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="12" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="10">
@@ -1819,11 +1204,11 @@
       <c r="K14" s="5">
         <v>110002</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="15" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="7"/>
       <c r="C15" s="5">
         <f t="shared" si="0"/>
@@ -1841,7 +1226,7 @@
       <c r="G15" s="5">
         <v>103</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="12" t="s">
         <v>34</v>
       </c>
       <c r="I15" s="10">
@@ -1853,11 +1238,11 @@
       <c r="K15" s="5">
         <v>110002</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="16" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B16" s="7"/>
       <c r="C16" s="5">
         <f t="shared" si="0"/>
@@ -1875,7 +1260,7 @@
       <c r="G16" s="5">
         <v>201</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="12" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="10">
@@ -1887,11 +1272,11 @@
       <c r="K16" s="5">
         <v>110002</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="17" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="7"/>
       <c r="C17" s="5">
         <f t="shared" si="0"/>
@@ -1909,7 +1294,7 @@
       <c r="G17" s="5">
         <v>202</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H17" s="12" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="10">
@@ -1921,11 +1306,11 @@
       <c r="K17" s="5">
         <v>110002</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="18" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="7"/>
       <c r="C18" s="5">
         <f t="shared" si="0"/>
@@ -1943,7 +1328,7 @@
       <c r="G18" s="5">
         <v>203</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="H18" s="12" t="s">
         <v>36</v>
       </c>
       <c r="I18" s="10">
@@ -1955,11 +1340,11 @@
       <c r="K18" s="5">
         <v>110002</v>
       </c>
-      <c r="L18" s="14" t="s">
+      <c r="L18" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="19" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="7"/>
       <c r="C19" s="5">
         <f t="shared" si="0"/>
@@ -1977,7 +1362,7 @@
       <c r="G19" s="5">
         <v>101</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H19" s="12" t="s">
         <v>37</v>
       </c>
       <c r="I19" s="10">
@@ -1989,11 +1374,11 @@
       <c r="K19" s="5">
         <v>110003</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L19" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="20" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="7"/>
       <c r="C20" s="5">
         <f t="shared" si="0"/>
@@ -2011,7 +1396,7 @@
       <c r="G20" s="5">
         <v>102</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="12" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="10">
@@ -2023,11 +1408,11 @@
       <c r="K20" s="5">
         <v>110003</v>
       </c>
-      <c r="L20" s="14" t="s">
+      <c r="L20" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="21" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="7"/>
       <c r="C21" s="5">
         <f t="shared" si="0"/>
@@ -2045,7 +1430,7 @@
       <c r="G21" s="5">
         <v>103</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="12" t="s">
         <v>39</v>
       </c>
       <c r="I21" s="10">
@@ -2057,11 +1442,11 @@
       <c r="K21" s="5">
         <v>110003</v>
       </c>
-      <c r="L21" s="14" t="s">
+      <c r="L21" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="22" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B22" s="7"/>
       <c r="C22" s="5">
         <f t="shared" si="0"/>
@@ -2079,7 +1464,7 @@
       <c r="G22" s="5">
         <v>201</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I22" s="10">
@@ -2091,11 +1476,11 @@
       <c r="K22" s="5">
         <v>110003</v>
       </c>
-      <c r="L22" s="14" t="s">
+      <c r="L22" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="23" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="7"/>
       <c r="C23" s="5">
         <f t="shared" si="0"/>
@@ -2113,7 +1498,7 @@
       <c r="G23" s="5">
         <v>202</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I23" s="10">
@@ -2125,11 +1510,11 @@
       <c r="K23" s="5">
         <v>110003</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="24" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="7"/>
       <c r="C24" s="5">
         <f t="shared" si="0"/>
@@ -2147,7 +1532,7 @@
       <c r="G24" s="5">
         <v>203</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I24" s="10">
@@ -2159,11 +1544,11 @@
       <c r="K24" s="5">
         <v>110003</v>
       </c>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="25" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B25" s="7"/>
       <c r="C25" s="5">
         <f t="shared" si="0"/>
@@ -2181,7 +1566,7 @@
       <c r="G25" s="5">
         <v>101</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="12" t="s">
         <v>42</v>
       </c>
       <c r="I25" s="10">
@@ -2193,11 +1578,11 @@
       <c r="K25" s="5">
         <v>110004</v>
       </c>
-      <c r="L25" s="14" t="s">
+      <c r="L25" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="26" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B26" s="7"/>
       <c r="C26" s="5">
         <f t="shared" si="0"/>
@@ -2215,7 +1600,7 @@
       <c r="G26" s="5">
         <v>102</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="12" t="s">
         <v>42</v>
       </c>
       <c r="I26" s="10">
@@ -2227,11 +1612,11 @@
       <c r="K26" s="5">
         <v>110004</v>
       </c>
-      <c r="L26" s="14" t="s">
+      <c r="L26" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="27" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B27" s="7"/>
       <c r="C27" s="5">
         <f t="shared" si="0"/>
@@ -2249,7 +1634,7 @@
       <c r="G27" s="5">
         <v>103</v>
       </c>
-      <c r="H27" s="13" t="s">
+      <c r="H27" s="12" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="10">
@@ -2261,11 +1646,11 @@
       <c r="K27" s="5">
         <v>110004</v>
       </c>
-      <c r="L27" s="14" t="s">
+      <c r="L27" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="28" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B28" s="7"/>
       <c r="C28" s="5">
         <f t="shared" si="0"/>
@@ -2283,7 +1668,7 @@
       <c r="G28" s="5">
         <v>201</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="12" t="s">
         <v>45</v>
       </c>
       <c r="I28" s="10">
@@ -2295,11 +1680,11 @@
       <c r="K28" s="5">
         <v>110004</v>
       </c>
-      <c r="L28" s="14" t="s">
+      <c r="L28" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="29" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B29" s="7"/>
       <c r="C29" s="5">
         <f t="shared" si="0"/>
@@ -2317,7 +1702,7 @@
       <c r="G29" s="5">
         <v>202</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H29" s="12" t="s">
         <v>45</v>
       </c>
       <c r="I29" s="10">
@@ -2329,11 +1714,11 @@
       <c r="K29" s="5">
         <v>110004</v>
       </c>
-      <c r="L29" s="14" t="s">
+      <c r="L29" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="30" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B30" s="7"/>
       <c r="C30" s="5">
         <f t="shared" si="0"/>
@@ -2351,7 +1736,7 @@
       <c r="G30" s="5">
         <v>203</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I30" s="10">
@@ -2363,11 +1748,11 @@
       <c r="K30" s="5">
         <v>110004</v>
       </c>
-      <c r="L30" s="14" t="s">
+      <c r="L30" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="31" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B31" s="7"/>
       <c r="C31" s="5">
         <f t="shared" si="0"/>
@@ -2385,10 +1770,10 @@
       <c r="G31" s="5">
         <v>101</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="14" t="s">
         <v>47</v>
       </c>
       <c r="J31" s="8">
@@ -2397,11 +1782,11 @@
       <c r="K31" s="5">
         <v>110005</v>
       </c>
-      <c r="L31" s="14" t="s">
+      <c r="L31" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="32" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B32" s="7"/>
       <c r="C32" s="5">
         <f t="shared" si="0"/>
@@ -2419,10 +1804,10 @@
       <c r="G32" s="5">
         <v>102</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="H32" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="14" t="s">
         <v>47</v>
       </c>
       <c r="J32" s="8">
@@ -2431,11 +1816,11 @@
       <c r="K32" s="5">
         <v>110005</v>
       </c>
-      <c r="L32" s="14" t="s">
+      <c r="L32" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="33" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B33" s="7"/>
       <c r="C33" s="5">
         <f t="shared" si="0"/>
@@ -2453,10 +1838,10 @@
       <c r="G33" s="5">
         <v>103</v>
       </c>
-      <c r="H33" s="13" t="s">
+      <c r="H33" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="14" t="s">
         <v>47</v>
       </c>
       <c r="J33" s="8">
@@ -2465,11 +1850,11 @@
       <c r="K33" s="5">
         <v>110005</v>
       </c>
-      <c r="L33" s="14" t="s">
+      <c r="L33" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="34" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B34" s="7"/>
       <c r="C34" s="5">
         <f t="shared" si="0"/>
@@ -2487,10 +1872,10 @@
       <c r="G34" s="5">
         <v>201</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="I34" s="14" t="s">
         <v>47</v>
       </c>
       <c r="J34" s="8">
@@ -2499,11 +1884,11 @@
       <c r="K34" s="5">
         <v>110005</v>
       </c>
-      <c r="L34" s="14" t="s">
+      <c r="L34" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="35" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B35" s="7"/>
       <c r="C35" s="5">
         <f t="shared" si="0"/>
@@ -2521,10 +1906,10 @@
       <c r="G35" s="5">
         <v>202</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H35" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="14" t="s">
         <v>47</v>
       </c>
       <c r="J35" s="8">
@@ -2533,11 +1918,11 @@
       <c r="K35" s="5">
         <v>110005</v>
       </c>
-      <c r="L35" s="14" t="s">
+      <c r="L35" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="36" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B36" s="7"/>
       <c r="C36" s="5">
         <f t="shared" si="0"/>
@@ -2555,10 +1940,10 @@
       <c r="G36" s="5">
         <v>203</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="H36" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="14" t="s">
         <v>47</v>
       </c>
       <c r="J36" s="8">
@@ -2567,11 +1952,11 @@
       <c r="K36" s="5">
         <v>110005</v>
       </c>
-      <c r="L36" s="14" t="s">
+      <c r="L36" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="37" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B37" s="7"/>
       <c r="C37" s="5">
         <f t="shared" si="0"/>
@@ -2589,10 +1974,10 @@
       <c r="G37" s="5">
         <v>101</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="I37" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J37" s="8">
@@ -2601,11 +1986,11 @@
       <c r="K37" s="5">
         <v>110006</v>
       </c>
-      <c r="L37" s="14" t="s">
+      <c r="L37" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="38" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B38" s="7"/>
       <c r="C38" s="5">
         <f t="shared" si="0"/>
@@ -2623,10 +2008,10 @@
       <c r="G38" s="5">
         <v>102</v>
       </c>
-      <c r="H38" s="13" t="s">
+      <c r="H38" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="I38" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J38" s="8">
@@ -2635,11 +2020,11 @@
       <c r="K38" s="5">
         <v>110006</v>
       </c>
-      <c r="L38" s="14" t="s">
+      <c r="L38" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="39" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B39" s="7"/>
       <c r="C39" s="5">
         <f t="shared" si="0"/>
@@ -2657,10 +2042,10 @@
       <c r="G39" s="5">
         <v>103</v>
       </c>
-      <c r="H39" s="13" t="s">
+      <c r="H39" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="8">
@@ -2669,11 +2054,11 @@
       <c r="K39" s="5">
         <v>110006</v>
       </c>
-      <c r="L39" s="14" t="s">
+      <c r="L39" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="40" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B40" s="7"/>
       <c r="C40" s="5">
         <f t="shared" si="0"/>
@@ -2691,10 +2076,10 @@
       <c r="G40" s="5">
         <v>201</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="8">
@@ -2703,11 +2088,11 @@
       <c r="K40" s="5">
         <v>110006</v>
       </c>
-      <c r="L40" s="14" t="s">
+      <c r="L40" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="41" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B41" s="7"/>
       <c r="C41" s="5">
         <f t="shared" si="0"/>
@@ -2725,10 +2110,10 @@
       <c r="G41" s="5">
         <v>202</v>
       </c>
-      <c r="H41" s="13" t="s">
+      <c r="H41" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="I41" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="8">
@@ -2737,11 +2122,11 @@
       <c r="K41" s="5">
         <v>110006</v>
       </c>
-      <c r="L41" s="14" t="s">
+      <c r="L41" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="42" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B42" s="7"/>
       <c r="C42" s="5">
         <f t="shared" si="0"/>
@@ -2759,10 +2144,10 @@
       <c r="G42" s="5">
         <v>203</v>
       </c>
-      <c r="H42" s="13" t="s">
+      <c r="H42" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="I42" s="14" t="s">
         <v>49</v>
       </c>
       <c r="J42" s="8">
@@ -2771,20 +2156,21 @@
       <c r="K42" s="5">
         <v>110006</v>
       </c>
-      <c r="L42" s="14" t="s">
+      <c r="L42" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="43" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B43" s="7"/>
       <c r="C43" s="5">
-        <v>3001</v>
+        <f t="shared" si="0"/>
+        <v>2701</v>
       </c>
       <c r="D43" s="5">
-        <v>20</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="F43" s="5">
         <v>1</v>
@@ -2792,30 +2178,33 @@
       <c r="G43" s="5">
         <v>101</v>
       </c>
-      <c r="H43" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I43" s="10">
-        <v>300300300300300</v>
-      </c>
-      <c r="J43" s="5">
-        <v>3</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="H43" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J43" s="8">
+        <v>2</v>
+      </c>
+      <c r="K43" s="16">
+        <v>110007</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B44" s="7"/>
       <c r="C44" s="5">
-        <v>3002</v>
+        <f t="shared" si="0"/>
+        <v>2702</v>
       </c>
       <c r="D44" s="5">
-        <v>20</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="F44" s="5">
         <v>1</v>
@@ -2823,30 +2212,33 @@
       <c r="G44" s="5">
         <v>102</v>
       </c>
-      <c r="H44" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I44" s="10">
-        <v>300300300300300</v>
-      </c>
-      <c r="J44" s="5">
-        <v>3</v>
-      </c>
-      <c r="K44" s="5"/>
-      <c r="L44" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="H44" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J44" s="8">
+        <v>2</v>
+      </c>
+      <c r="K44" s="16">
+        <v>110007</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B45" s="7"/>
       <c r="C45" s="5">
-        <v>3003</v>
+        <f t="shared" si="0"/>
+        <v>2703</v>
       </c>
       <c r="D45" s="5">
-        <v>20</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="F45" s="5">
         <v>1</v>
@@ -2854,30 +2246,33 @@
       <c r="G45" s="5">
         <v>103</v>
       </c>
-      <c r="H45" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I45" s="10">
-        <v>300300300300300</v>
-      </c>
-      <c r="J45" s="5">
-        <v>3</v>
-      </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="H45" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J45" s="8">
+        <v>2</v>
+      </c>
+      <c r="K45" s="16">
+        <v>110007</v>
+      </c>
+      <c r="L45" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B46" s="7"/>
       <c r="C46" s="5">
-        <v>3004</v>
+        <f t="shared" si="0"/>
+        <v>2704</v>
       </c>
       <c r="D46" s="5">
-        <v>20</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="F46" s="5">
         <v>2</v>
@@ -2885,30 +2280,33 @@
       <c r="G46" s="5">
         <v>201</v>
       </c>
-      <c r="H46" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="10">
-        <v>300300300300300</v>
-      </c>
-      <c r="J46" s="5">
-        <v>3</v>
-      </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="H46" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J46" s="8">
+        <v>2</v>
+      </c>
+      <c r="K46" s="16">
+        <v>110007</v>
+      </c>
+      <c r="L46" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B47" s="7"/>
       <c r="C47" s="5">
-        <v>3005</v>
+        <f t="shared" si="0"/>
+        <v>2705</v>
       </c>
       <c r="D47" s="5">
-        <v>20</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="F47" s="5">
         <v>2</v>
@@ -2916,30 +2314,33 @@
       <c r="G47" s="5">
         <v>202</v>
       </c>
-      <c r="H47" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="10">
-        <v>300300300300300</v>
-      </c>
-      <c r="J47" s="5">
-        <v>3</v>
-      </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="H47" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J47" s="8">
+        <v>2</v>
+      </c>
+      <c r="K47" s="16">
+        <v>110007</v>
+      </c>
+      <c r="L47" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B48" s="7"/>
       <c r="C48" s="5">
-        <v>3006</v>
+        <f t="shared" si="0"/>
+        <v>2706</v>
       </c>
       <c r="D48" s="5">
-        <v>20</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>50</v>
+        <v>70</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="F48" s="5">
         <v>2</v>
@@ -2947,30 +2348,32 @@
       <c r="G48" s="5">
         <v>203</v>
       </c>
-      <c r="H48" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="10">
-        <v>300300300300300</v>
-      </c>
-      <c r="J48" s="5">
-        <v>3</v>
-      </c>
-      <c r="K48" s="5"/>
-      <c r="L48" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="H48" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J48" s="8">
+        <v>2</v>
+      </c>
+      <c r="K48" s="16">
+        <v>110007</v>
+      </c>
+      <c r="L48" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B49" s="7"/>
       <c r="C49" s="5">
-        <v>3051</v>
+        <v>3001</v>
       </c>
       <c r="D49" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F49" s="5">
         <v>1</v>
@@ -2978,30 +2381,30 @@
       <c r="G49" s="5">
         <v>101</v>
       </c>
-      <c r="H49" s="13" t="s">
-        <v>32</v>
+      <c r="H49" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="I49" s="10">
-        <v>900900900900900</v>
+        <v>300300300300300</v>
       </c>
       <c r="J49" s="5">
         <v>3</v>
       </c>
       <c r="K49" s="5"/>
-      <c r="L49" s="16" t="s">
+      <c r="L49" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="50" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B50" s="7"/>
       <c r="C50" s="5">
-        <v>3052</v>
+        <v>3002</v>
       </c>
       <c r="D50" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F50" s="5">
         <v>1</v>
@@ -3009,30 +2412,30 @@
       <c r="G50" s="5">
         <v>102</v>
       </c>
-      <c r="H50" s="13" t="s">
-        <v>32</v>
+      <c r="H50" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="I50" s="10">
-        <v>900900900900900</v>
+        <v>300300300300300</v>
       </c>
       <c r="J50" s="5">
         <v>3</v>
       </c>
       <c r="K50" s="5"/>
-      <c r="L50" s="16" t="s">
+      <c r="L50" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="51" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B51" s="7"/>
       <c r="C51" s="5">
-        <v>3053</v>
+        <v>3003</v>
       </c>
       <c r="D51" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F51" s="5">
         <v>1</v>
@@ -3040,30 +2443,30 @@
       <c r="G51" s="5">
         <v>103</v>
       </c>
-      <c r="H51" s="13" t="s">
-        <v>34</v>
+      <c r="H51" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="I51" s="10">
-        <v>900900900900900</v>
+        <v>300300300300300</v>
       </c>
       <c r="J51" s="5">
         <v>3</v>
       </c>
       <c r="K51" s="5"/>
-      <c r="L51" s="16" t="s">
+      <c r="L51" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="52" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B52" s="7"/>
       <c r="C52" s="5">
-        <v>3054</v>
+        <v>3004</v>
       </c>
       <c r="D52" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F52" s="5">
         <v>2</v>
@@ -3071,30 +2474,30 @@
       <c r="G52" s="5">
         <v>201</v>
       </c>
-      <c r="H52" s="13" t="s">
-        <v>35</v>
+      <c r="H52" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="I52" s="10">
-        <v>900900900900900</v>
+        <v>300300300300300</v>
       </c>
       <c r="J52" s="5">
         <v>3</v>
       </c>
       <c r="K52" s="5"/>
-      <c r="L52" s="16" t="s">
+      <c r="L52" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="53" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B53" s="7"/>
       <c r="C53" s="5">
-        <v>3055</v>
+        <v>3005</v>
       </c>
       <c r="D53" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F53" s="5">
         <v>2</v>
@@ -3102,30 +2505,30 @@
       <c r="G53" s="5">
         <v>202</v>
       </c>
-      <c r="H53" s="13" t="s">
-        <v>35</v>
+      <c r="H53" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="I53" s="10">
-        <v>900900900900900</v>
+        <v>300300300300300</v>
       </c>
       <c r="J53" s="5">
         <v>3</v>
       </c>
       <c r="K53" s="5"/>
-      <c r="L53" s="16" t="s">
+      <c r="L53" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="54" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B54" s="7"/>
       <c r="C54" s="5">
-        <v>3056</v>
+        <v>3006</v>
       </c>
       <c r="D54" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F54" s="5">
         <v>2</v>
@@ -3133,30 +2536,30 @@
       <c r="G54" s="5">
         <v>203</v>
       </c>
-      <c r="H54" s="13" t="s">
-        <v>36</v>
+      <c r="H54" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="I54" s="10">
-        <v>900900900900900</v>
+        <v>300300300300300</v>
       </c>
       <c r="J54" s="5">
         <v>3</v>
       </c>
       <c r="K54" s="5"/>
-      <c r="L54" s="16" t="s">
+      <c r="L54" s="15" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="55" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B55" s="7"/>
       <c r="C55" s="5">
-        <v>5101</v>
+        <v>3051</v>
       </c>
       <c r="D55" s="5">
-        <v>20</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="F55" s="5">
         <v>1</v>
@@ -3164,30 +2567,30 @@
       <c r="G55" s="5">
         <v>101</v>
       </c>
-      <c r="H55" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>54</v>
+      <c r="H55" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" s="10">
+        <v>900900900900900</v>
       </c>
       <c r="J55" s="5">
-        <v>4</v>
-      </c>
-      <c r="K55" s="11">
-        <v>72000002</v>
-      </c>
-      <c r="L55" s="11"/>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+        <v>3</v>
+      </c>
+      <c r="K55" s="5"/>
+      <c r="L55" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B56" s="7"/>
       <c r="C56" s="5">
-        <v>5102</v>
+        <v>3052</v>
       </c>
       <c r="D56" s="5">
-        <v>20</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="F56" s="5">
         <v>1</v>
@@ -3195,30 +2598,30 @@
       <c r="G56" s="5">
         <v>102</v>
       </c>
-      <c r="H56" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>54</v>
+      <c r="H56" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I56" s="10">
+        <v>900900900900900</v>
       </c>
       <c r="J56" s="5">
-        <v>4</v>
-      </c>
-      <c r="K56" s="11">
-        <v>72000002</v>
-      </c>
-      <c r="L56" s="11"/>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+        <v>3</v>
+      </c>
+      <c r="K56" s="5"/>
+      <c r="L56" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B57" s="7"/>
       <c r="C57" s="5">
-        <v>5103</v>
+        <v>3053</v>
       </c>
       <c r="D57" s="5">
-        <v>20</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="F57" s="5">
         <v>1</v>
@@ -3226,30 +2629,30 @@
       <c r="G57" s="5">
         <v>103</v>
       </c>
-      <c r="H57" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>54</v>
+      <c r="H57" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I57" s="10">
+        <v>900900900900900</v>
       </c>
       <c r="J57" s="5">
-        <v>4</v>
-      </c>
-      <c r="K57" s="11">
-        <v>72000002</v>
-      </c>
-      <c r="L57" s="11"/>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+        <v>3</v>
+      </c>
+      <c r="K57" s="5"/>
+      <c r="L57" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B58" s="7"/>
       <c r="C58" s="5">
-        <v>5104</v>
+        <v>3054</v>
       </c>
       <c r="D58" s="5">
-        <v>20</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="F58" s="5">
         <v>2</v>
@@ -3257,30 +2660,30 @@
       <c r="G58" s="5">
         <v>201</v>
       </c>
-      <c r="H58" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>54</v>
+      <c r="H58" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58" s="10">
+        <v>900900900900900</v>
       </c>
       <c r="J58" s="5">
-        <v>4</v>
-      </c>
-      <c r="K58" s="11">
-        <v>72000002</v>
-      </c>
-      <c r="L58" s="11"/>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+        <v>3</v>
+      </c>
+      <c r="K58" s="5"/>
+      <c r="L58" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B59" s="7"/>
       <c r="C59" s="5">
-        <v>5105</v>
+        <v>3055</v>
       </c>
       <c r="D59" s="5">
-        <v>20</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="F59" s="5">
         <v>2</v>
@@ -3288,30 +2691,30 @@
       <c r="G59" s="5">
         <v>202</v>
       </c>
-      <c r="H59" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>54</v>
+      <c r="H59" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59" s="10">
+        <v>900900900900900</v>
       </c>
       <c r="J59" s="5">
-        <v>4</v>
-      </c>
-      <c r="K59" s="11">
-        <v>72000002</v>
-      </c>
-      <c r="L59" s="11"/>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+        <v>3</v>
+      </c>
+      <c r="K59" s="5"/>
+      <c r="L59" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B60" s="7"/>
       <c r="C60" s="5">
-        <v>5106</v>
+        <v>3056</v>
       </c>
       <c r="D60" s="5">
-        <v>20</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="F60" s="5">
         <v>2</v>
@@ -3319,27 +2722,27 @@
       <c r="G60" s="5">
         <v>203</v>
       </c>
-      <c r="H60" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>54</v>
+      <c r="H60" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I60" s="10">
+        <v>900900900900900</v>
       </c>
       <c r="J60" s="5">
-        <v>4</v>
-      </c>
-      <c r="K60" s="11">
-        <v>72000002</v>
-      </c>
-      <c r="L60" s="11"/>
-    </row>
-    <row r="61" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+        <v>3</v>
+      </c>
+      <c r="K60" s="5"/>
+      <c r="L60" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B61" s="7"/>
       <c r="C61" s="5">
-        <v>5201</v>
+        <v>5101</v>
       </c>
       <c r="D61" s="5">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>53</v>
@@ -3350,27 +2753,27 @@
       <c r="G61" s="5">
         <v>101</v>
       </c>
-      <c r="H61" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I61" s="10">
-        <v>100100100100100</v>
+      <c r="H61" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="J61" s="5">
         <v>4</v>
       </c>
       <c r="K61" s="11">
-        <v>72000003</v>
+        <v>72000002</v>
       </c>
       <c r="L61" s="11"/>
     </row>
-    <row r="62" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="62" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B62" s="7"/>
       <c r="C62" s="5">
-        <v>5202</v>
+        <v>5102</v>
       </c>
       <c r="D62" s="5">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>53</v>
@@ -3381,27 +2784,27 @@
       <c r="G62" s="5">
         <v>102</v>
       </c>
-      <c r="H62" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I62" s="10">
-        <v>100100100100100</v>
+      <c r="H62" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="J62" s="5">
         <v>4</v>
       </c>
       <c r="K62" s="11">
-        <v>72000003</v>
+        <v>72000002</v>
       </c>
       <c r="L62" s="11"/>
     </row>
-    <row r="63" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="63" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B63" s="7"/>
       <c r="C63" s="5">
-        <v>5203</v>
+        <v>5103</v>
       </c>
       <c r="D63" s="5">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>53</v>
@@ -3412,27 +2815,27 @@
       <c r="G63" s="5">
         <v>103</v>
       </c>
-      <c r="H63" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I63" s="10">
-        <v>100100100100100</v>
+      <c r="H63" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="J63" s="5">
         <v>4</v>
       </c>
       <c r="K63" s="11">
-        <v>72000003</v>
+        <v>72000002</v>
       </c>
       <c r="L63" s="11"/>
     </row>
-    <row r="64" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="64" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B64" s="7"/>
       <c r="C64" s="5">
-        <v>5204</v>
+        <v>5104</v>
       </c>
       <c r="D64" s="5">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>53</v>
@@ -3443,27 +2846,27 @@
       <c r="G64" s="5">
         <v>201</v>
       </c>
-      <c r="H64" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I64" s="10">
-        <v>100100100100100</v>
+      <c r="H64" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="J64" s="5">
         <v>4</v>
       </c>
       <c r="K64" s="11">
-        <v>72000003</v>
+        <v>72000002</v>
       </c>
       <c r="L64" s="11"/>
     </row>
-    <row r="65" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="65" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B65" s="7"/>
       <c r="C65" s="5">
-        <v>5205</v>
+        <v>5105</v>
       </c>
       <c r="D65" s="5">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>53</v>
@@ -3474,27 +2877,27 @@
       <c r="G65" s="5">
         <v>202</v>
       </c>
-      <c r="H65" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I65" s="10">
-        <v>100100100100100</v>
+      <c r="H65" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="J65" s="5">
         <v>4</v>
       </c>
       <c r="K65" s="11">
-        <v>72000003</v>
+        <v>72000002</v>
       </c>
       <c r="L65" s="11"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="66" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B66" s="7"/>
       <c r="C66" s="5">
-        <v>5206</v>
+        <v>5106</v>
       </c>
       <c r="D66" s="5">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>53</v>
@@ -3505,27 +2908,27 @@
       <c r="G66" s="5">
         <v>203</v>
       </c>
-      <c r="H66" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="I66" s="10">
-        <v>100100100100100</v>
+      <c r="H66" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="J66" s="5">
         <v>4</v>
       </c>
       <c r="K66" s="11">
-        <v>72000003</v>
+        <v>72000002</v>
       </c>
       <c r="L66" s="11"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="67" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B67" s="7"/>
       <c r="C67" s="5">
-        <v>5301</v>
+        <v>5201</v>
       </c>
       <c r="D67" s="5">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>53</v>
@@ -3536,27 +2939,27 @@
       <c r="G67" s="5">
         <v>101</v>
       </c>
-      <c r="H67" s="13" t="s">
-        <v>37</v>
+      <c r="H67" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="I67" s="10">
-        <v>150150150150150</v>
+        <v>100100100100100</v>
       </c>
       <c r="J67" s="5">
         <v>4</v>
       </c>
       <c r="K67" s="11">
-        <v>72000004</v>
+        <v>72000003</v>
       </c>
       <c r="L67" s="11"/>
     </row>
-    <row r="68" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="68" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B68" s="7"/>
       <c r="C68" s="5">
-        <v>5302</v>
+        <v>5202</v>
       </c>
       <c r="D68" s="5">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>53</v>
@@ -3567,27 +2970,27 @@
       <c r="G68" s="5">
         <v>102</v>
       </c>
-      <c r="H68" s="13" t="s">
-        <v>37</v>
+      <c r="H68" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="I68" s="10">
-        <v>150150150150150</v>
+        <v>100100100100100</v>
       </c>
       <c r="J68" s="5">
         <v>4</v>
       </c>
       <c r="K68" s="11">
-        <v>72000004</v>
+        <v>72000003</v>
       </c>
       <c r="L68" s="11"/>
     </row>
-    <row r="69" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="69" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B69" s="7"/>
       <c r="C69" s="5">
-        <v>5303</v>
+        <v>5203</v>
       </c>
       <c r="D69" s="5">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>53</v>
@@ -3598,27 +3001,27 @@
       <c r="G69" s="5">
         <v>103</v>
       </c>
-      <c r="H69" s="13" t="s">
-        <v>39</v>
+      <c r="H69" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="I69" s="10">
-        <v>150150150150150</v>
+        <v>100100100100100</v>
       </c>
       <c r="J69" s="5">
         <v>4</v>
       </c>
       <c r="K69" s="11">
-        <v>72000004</v>
+        <v>72000003</v>
       </c>
       <c r="L69" s="11"/>
     </row>
-    <row r="70" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="70" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B70" s="7"/>
       <c r="C70" s="5">
-        <v>5304</v>
+        <v>5204</v>
       </c>
       <c r="D70" s="5">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>53</v>
@@ -3629,27 +3032,27 @@
       <c r="G70" s="5">
         <v>201</v>
       </c>
-      <c r="H70" s="13" t="s">
-        <v>40</v>
+      <c r="H70" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="I70" s="10">
-        <v>150150150150150</v>
+        <v>100100100100100</v>
       </c>
       <c r="J70" s="5">
         <v>4</v>
       </c>
       <c r="K70" s="11">
-        <v>72000004</v>
+        <v>72000003</v>
       </c>
       <c r="L70" s="11"/>
     </row>
-    <row r="71" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="71" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B71" s="7"/>
       <c r="C71" s="5">
-        <v>5305</v>
+        <v>5205</v>
       </c>
       <c r="D71" s="5">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>53</v>
@@ -3660,27 +3063,27 @@
       <c r="G71" s="5">
         <v>202</v>
       </c>
-      <c r="H71" s="13" t="s">
-        <v>40</v>
+      <c r="H71" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="I71" s="10">
-        <v>150150150150150</v>
+        <v>100100100100100</v>
       </c>
       <c r="J71" s="5">
         <v>4</v>
       </c>
       <c r="K71" s="11">
-        <v>72000004</v>
+        <v>72000003</v>
       </c>
       <c r="L71" s="11"/>
     </row>
-    <row r="72" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="72" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B72" s="7"/>
       <c r="C72" s="5">
-        <v>5306</v>
+        <v>5206</v>
       </c>
       <c r="D72" s="5">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>53</v>
@@ -3691,27 +3094,27 @@
       <c r="G72" s="5">
         <v>203</v>
       </c>
-      <c r="H72" s="13" t="s">
-        <v>41</v>
+      <c r="H72" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="I72" s="10">
-        <v>150150150150150</v>
+        <v>100100100100100</v>
       </c>
       <c r="J72" s="5">
         <v>4</v>
       </c>
       <c r="K72" s="11">
-        <v>72000004</v>
+        <v>72000003</v>
       </c>
       <c r="L72" s="11"/>
     </row>
-    <row r="73" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="73" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B73" s="7"/>
       <c r="C73" s="5">
-        <v>5401</v>
+        <v>5301</v>
       </c>
       <c r="D73" s="5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>53</v>
@@ -3722,27 +3125,27 @@
       <c r="G73" s="5">
         <v>101</v>
       </c>
-      <c r="H73" s="13" t="s">
-        <v>42</v>
+      <c r="H73" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="I73" s="10">
-        <v>200200200200200</v>
+        <v>150150150150150</v>
       </c>
       <c r="J73" s="5">
         <v>4</v>
       </c>
       <c r="K73" s="11">
-        <v>72000005</v>
+        <v>72000004</v>
       </c>
       <c r="L73" s="11"/>
     </row>
-    <row r="74" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="74" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B74" s="7"/>
       <c r="C74" s="5">
-        <v>5402</v>
+        <v>5302</v>
       </c>
       <c r="D74" s="5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>53</v>
@@ -3753,27 +3156,27 @@
       <c r="G74" s="5">
         <v>102</v>
       </c>
-      <c r="H74" s="13" t="s">
-        <v>42</v>
+      <c r="H74" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="I74" s="10">
-        <v>200200200200200</v>
+        <v>150150150150150</v>
       </c>
       <c r="J74" s="5">
         <v>4</v>
       </c>
       <c r="K74" s="11">
-        <v>72000005</v>
+        <v>72000004</v>
       </c>
       <c r="L74" s="11"/>
     </row>
-    <row r="75" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="75" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B75" s="7"/>
       <c r="C75" s="5">
-        <v>5403</v>
+        <v>5303</v>
       </c>
       <c r="D75" s="5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>53</v>
@@ -3784,27 +3187,27 @@
       <c r="G75" s="5">
         <v>103</v>
       </c>
-      <c r="H75" s="13" t="s">
-        <v>44</v>
+      <c r="H75" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="I75" s="10">
-        <v>200200200200200</v>
+        <v>150150150150150</v>
       </c>
       <c r="J75" s="5">
         <v>4</v>
       </c>
       <c r="K75" s="11">
-        <v>72000005</v>
+        <v>72000004</v>
       </c>
       <c r="L75" s="11"/>
     </row>
-    <row r="76" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="76" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B76" s="7"/>
       <c r="C76" s="5">
-        <v>5404</v>
+        <v>5304</v>
       </c>
       <c r="D76" s="5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>53</v>
@@ -3815,27 +3218,27 @@
       <c r="G76" s="5">
         <v>201</v>
       </c>
-      <c r="H76" s="13" t="s">
-        <v>45</v>
+      <c r="H76" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="I76" s="10">
-        <v>200200200200200</v>
+        <v>150150150150150</v>
       </c>
       <c r="J76" s="5">
         <v>4</v>
       </c>
       <c r="K76" s="11">
-        <v>72000005</v>
+        <v>72000004</v>
       </c>
       <c r="L76" s="11"/>
     </row>
-    <row r="77" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="77" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B77" s="7"/>
       <c r="C77" s="5">
-        <v>5405</v>
+        <v>5305</v>
       </c>
       <c r="D77" s="5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>53</v>
@@ -3846,27 +3249,27 @@
       <c r="G77" s="5">
         <v>202</v>
       </c>
-      <c r="H77" s="13" t="s">
-        <v>45</v>
+      <c r="H77" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="I77" s="10">
-        <v>200200200200200</v>
+        <v>150150150150150</v>
       </c>
       <c r="J77" s="5">
         <v>4</v>
       </c>
       <c r="K77" s="11">
-        <v>72000005</v>
+        <v>72000004</v>
       </c>
       <c r="L77" s="11"/>
     </row>
-    <row r="78" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="78" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B78" s="7"/>
       <c r="C78" s="5">
-        <v>5406</v>
+        <v>5306</v>
       </c>
       <c r="D78" s="5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>53</v>
@@ -3877,228 +3280,414 @@
       <c r="G78" s="5">
         <v>203</v>
       </c>
-      <c r="H78" s="13" t="s">
-        <v>46</v>
+      <c r="H78" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="I78" s="10">
-        <v>200200200200200</v>
+        <v>150150150150150</v>
       </c>
       <c r="J78" s="5">
         <v>4</v>
       </c>
       <c r="K78" s="11">
-        <v>72000005</v>
+        <v>72000004</v>
       </c>
       <c r="L78" s="11"/>
     </row>
-    <row r="79" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="79" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B79" s="7"/>
       <c r="C79" s="5">
-        <v>5001</v>
+        <v>5401</v>
       </c>
       <c r="D79" s="5">
-        <v>30</v>
-      </c>
-      <c r="E79" s="5" t="s">
         <v>55</v>
       </c>
+      <c r="E79" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="F79" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" s="5">
-        <v>203</v>
-      </c>
-      <c r="H79" s="13" t="s">
-        <v>36</v>
+        <v>101</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="I79" s="10">
-        <v>100100100100100</v>
+        <v>200200200200200</v>
       </c>
       <c r="J79" s="5">
-        <v>5</v>
-      </c>
-      <c r="K79" s="5"/>
-      <c r="L79" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="80" ht="20.1" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K79" s="11">
+        <v>72000005</v>
+      </c>
+      <c r="L79" s="11"/>
+    </row>
+    <row r="80" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B80" s="7"/>
       <c r="C80" s="5">
-        <v>6001</v>
+        <v>5402</v>
       </c>
       <c r="D80" s="5">
-        <v>40</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F80" s="3">
-        <v>2</v>
-      </c>
-      <c r="G80" s="3">
-        <v>203</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>36</v>
+        <v>55</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F80" s="5">
+        <v>1</v>
+      </c>
+      <c r="G80" s="5">
+        <v>102</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="I80" s="10">
         <v>200200200200200</v>
       </c>
-      <c r="J80" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="J80" s="5">
+        <v>4</v>
+      </c>
+      <c r="K80" s="11">
+        <v>72000005</v>
+      </c>
+      <c r="L80" s="11"/>
+    </row>
+    <row r="81" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B81" s="7"/>
       <c r="C81" s="5">
-        <v>7001</v>
+        <v>5403</v>
       </c>
       <c r="D81" s="5">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F81" s="5">
         <v>1</v>
       </c>
       <c r="G81" s="5">
-        <v>0</v>
-      </c>
-      <c r="H81" s="5"/>
-      <c r="I81" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J81" s="8">
-        <v>7</v>
-      </c>
-      <c r="K81" s="5"/>
-      <c r="L81" s="9"/>
-    </row>
-    <row r="82" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+        <v>103</v>
+      </c>
+      <c r="H81" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I81" s="10">
+        <v>200200200200200</v>
+      </c>
+      <c r="J81" s="5">
+        <v>4</v>
+      </c>
+      <c r="K81" s="11">
+        <v>72000005</v>
+      </c>
+      <c r="L81" s="11"/>
+    </row>
+    <row r="82" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B82" s="7"/>
       <c r="C82" s="5">
-        <v>8001</v>
+        <v>5404</v>
       </c>
       <c r="D82" s="5">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F82" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82" s="5">
-        <v>0</v>
-      </c>
-      <c r="H82" s="5"/>
-      <c r="I82" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J82" s="8">
-        <v>8</v>
-      </c>
-      <c r="K82" s="5"/>
-      <c r="L82" s="9"/>
-    </row>
-    <row r="83" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+        <v>201</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I82" s="10">
+        <v>200200200200200</v>
+      </c>
+      <c r="J82" s="5">
+        <v>4</v>
+      </c>
+      <c r="K82" s="11">
+        <v>72000005</v>
+      </c>
+      <c r="L82" s="11"/>
+    </row>
+    <row r="83" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B83" s="7"/>
       <c r="C83" s="5">
-        <v>9001</v>
+        <v>5405</v>
       </c>
       <c r="D83" s="5">
         <v>55</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F83" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" s="5">
-        <v>0</v>
-      </c>
-      <c r="H83" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="H83" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I83" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J83" s="8">
-        <v>9</v>
-      </c>
-      <c r="K83" s="5"/>
-      <c r="L83" s="14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="I83" s="10">
+        <v>200200200200200</v>
+      </c>
+      <c r="J83" s="5">
+        <v>4</v>
+      </c>
+      <c r="K83" s="11">
+        <v>72000005</v>
+      </c>
+      <c r="L83" s="11"/>
+    </row>
+    <row r="84" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B84" s="7"/>
       <c r="C84" s="5">
-        <v>10001</v>
+        <v>5406</v>
       </c>
       <c r="D84" s="5">
         <v>55</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F84" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" s="5">
-        <v>0</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="I84" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J84" s="8">
-        <v>10</v>
-      </c>
-      <c r="K84" s="5"/>
-      <c r="L84" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+        <v>203</v>
+      </c>
+      <c r="H84" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I84" s="10">
+        <v>200200200200200</v>
+      </c>
+      <c r="J84" s="5">
+        <v>4</v>
+      </c>
+      <c r="K84" s="11">
+        <v>72000005</v>
+      </c>
+      <c r="L84" s="11"/>
+    </row>
+    <row r="85" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B85" s="7"/>
       <c r="C85" s="5">
+        <v>5001</v>
+      </c>
+      <c r="D85" s="5">
+        <v>30</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" s="5">
+        <v>2</v>
+      </c>
+      <c r="G85" s="5">
+        <v>203</v>
+      </c>
+      <c r="H85" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I85" s="10">
+        <v>100100100100100</v>
+      </c>
+      <c r="J85" s="5">
+        <v>5</v>
+      </c>
+      <c r="K85" s="5"/>
+      <c r="L85" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="C86" s="5">
+        <v>6001</v>
+      </c>
+      <c r="D86" s="5">
+        <v>40</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F86" s="3">
+        <v>2</v>
+      </c>
+      <c r="G86" s="3">
+        <v>203</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I86" s="10">
+        <v>200200200200200</v>
+      </c>
+      <c r="J86" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B87" s="7"/>
+      <c r="C87" s="5">
+        <v>7001</v>
+      </c>
+      <c r="D87" s="5">
+        <v>20</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F87" s="5">
+        <v>1</v>
+      </c>
+      <c r="G87" s="5">
+        <v>0</v>
+      </c>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" s="8">
+        <v>7</v>
+      </c>
+      <c r="K87" s="5"/>
+      <c r="L87" s="9"/>
+    </row>
+    <row r="88" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B88" s="7"/>
+      <c r="C88" s="5">
+        <v>8001</v>
+      </c>
+      <c r="D88" s="5">
+        <v>20</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F88" s="5">
+        <v>1</v>
+      </c>
+      <c r="G88" s="5">
+        <v>0</v>
+      </c>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" s="8">
+        <v>8</v>
+      </c>
+      <c r="K88" s="5"/>
+      <c r="L88" s="9"/>
+    </row>
+    <row r="89" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B89" s="7"/>
+      <c r="C89" s="5">
+        <v>9001</v>
+      </c>
+      <c r="D89" s="5">
+        <v>55</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F89" s="5">
+        <v>1</v>
+      </c>
+      <c r="G89" s="5">
+        <v>0</v>
+      </c>
+      <c r="H89" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" s="8">
+        <v>9</v>
+      </c>
+      <c r="K89" s="5"/>
+      <c r="L89" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B90" s="7"/>
+      <c r="C90" s="5">
+        <v>10001</v>
+      </c>
+      <c r="D90" s="5">
+        <v>55</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F90" s="5">
+        <v>1</v>
+      </c>
+      <c r="G90" s="5">
+        <v>0</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" s="8">
+        <v>10</v>
+      </c>
+      <c r="K90" s="5"/>
+      <c r="L90" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="91" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B91" s="7"/>
+      <c r="C91" s="5">
         <v>11001</v>
       </c>
-      <c r="D85" s="5">
-        <v>1</v>
-      </c>
-      <c r="E85" s="8" t="s">
+      <c r="D91" s="5">
+        <v>1</v>
+      </c>
+      <c r="E91" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F85" s="5">
-        <v>1</v>
-      </c>
-      <c r="G85" s="5">
+      <c r="F91" s="5">
+        <v>1</v>
+      </c>
+      <c r="G91" s="5">
         <v>0</v>
       </c>
-      <c r="H85" s="13" t="s">
+      <c r="H91" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I85" s="5" t="s">
+      <c r="I91" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J85" s="8">
+      <c r="J91" s="8">
         <v>11</v>
       </c>
-      <c r="K85" s="5"/>
-      <c r="L85" s="14" t="s">
+      <c r="K91" s="5"/>
+      <c r="L91" s="13" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/RobotConfig.xlsx
+++ b/Excel/RobotConfig.xlsx
@@ -1,32 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3432DD56-A32F-40F3-87D9-2AC3B1CAD8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="809"/>
   </bookViews>
   <sheets>
     <sheet name="RobotConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -48,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="J3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -79,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="K3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -101,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -325,8 +332,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,13 +349,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -367,10 +373,154 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -378,21 +528,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -411,8 +553,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -433,74 +761,363 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 6" xfId="50"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -758,12 +1375,12 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -781,7 +1398,7 @@
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -797,7 +1414,7 @@
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -813,7 +1430,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
@@ -847,7 +1464,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
@@ -881,7 +1498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
@@ -915,7 +1532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B6" s="7"/>
       <c r="C6" s="5">
         <v>1001</v>
@@ -942,7 +1559,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="9"/>
     </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B7" s="7"/>
       <c r="C7" s="5">
         <v>2101</v>
@@ -959,7 +1576,7 @@
       <c r="G7" s="5">
         <v>101</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I7" s="10">
@@ -971,11 +1588,11 @@
       <c r="K7" s="5">
         <v>110001</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B8" s="7"/>
       <c r="C8" s="5">
         <v>2102</v>
@@ -992,7 +1609,7 @@
       <c r="G8" s="5">
         <v>102</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="10">
@@ -1004,11 +1621,11 @@
       <c r="K8" s="5">
         <v>110001</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="L8" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B9" s="7"/>
       <c r="C9" s="5">
         <v>2103</v>
@@ -1025,7 +1642,7 @@
       <c r="G9" s="5">
         <v>103</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="14" t="s">
         <v>29</v>
       </c>
       <c r="I9" s="10">
@@ -1037,11 +1654,11 @@
       <c r="K9" s="5">
         <v>110001</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B10" s="7"/>
       <c r="C10" s="5">
         <v>2104</v>
@@ -1058,7 +1675,7 @@
       <c r="G10" s="5">
         <v>201</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="10">
@@ -1070,11 +1687,11 @@
       <c r="K10" s="5">
         <v>110001</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B11" s="7"/>
       <c r="C11" s="5">
         <v>2105</v>
@@ -1091,7 +1708,7 @@
       <c r="G11" s="5">
         <v>202</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="10">
@@ -1103,11 +1720,11 @@
       <c r="K11" s="5">
         <v>110001</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B12" s="7"/>
       <c r="C12" s="5">
         <v>2106</v>
@@ -1124,7 +1741,7 @@
       <c r="G12" s="5">
         <v>203</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="10">
@@ -1136,11 +1753,11 @@
       <c r="K12" s="5">
         <v>110001</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B13" s="7"/>
       <c r="C13" s="5">
         <f>C7+100</f>
@@ -1158,7 +1775,7 @@
       <c r="G13" s="5">
         <v>101</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="10">
@@ -1170,11 +1787,11 @@
       <c r="K13" s="5">
         <v>110002</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B14" s="7"/>
       <c r="C14" s="5">
         <f t="shared" ref="C14:C48" si="0">C8+100</f>
@@ -1192,7 +1809,7 @@
       <c r="G14" s="5">
         <v>102</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="10">
@@ -1204,11 +1821,11 @@
       <c r="K14" s="5">
         <v>110002</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B15" s="7"/>
       <c r="C15" s="5">
         <f t="shared" si="0"/>
@@ -1226,7 +1843,7 @@
       <c r="G15" s="5">
         <v>103</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="14" t="s">
         <v>34</v>
       </c>
       <c r="I15" s="10">
@@ -1238,11 +1855,11 @@
       <c r="K15" s="5">
         <v>110002</v>
       </c>
-      <c r="L15" s="13" t="s">
+      <c r="L15" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B16" s="7"/>
       <c r="C16" s="5">
         <f t="shared" si="0"/>
@@ -1260,7 +1877,7 @@
       <c r="G16" s="5">
         <v>201</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="10">
@@ -1272,11 +1889,11 @@
       <c r="K16" s="5">
         <v>110002</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="L16" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B17" s="7"/>
       <c r="C17" s="5">
         <f t="shared" si="0"/>
@@ -1294,7 +1911,7 @@
       <c r="G17" s="5">
         <v>202</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="10">
@@ -1306,11 +1923,11 @@
       <c r="K17" s="5">
         <v>110002</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="L17" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B18" s="7"/>
       <c r="C18" s="5">
         <f t="shared" si="0"/>
@@ -1328,7 +1945,7 @@
       <c r="G18" s="5">
         <v>203</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I18" s="10">
@@ -1340,11 +1957,11 @@
       <c r="K18" s="5">
         <v>110002</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="L18" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="19" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B19" s="7"/>
       <c r="C19" s="5">
         <f t="shared" si="0"/>
@@ -1362,7 +1979,7 @@
       <c r="G19" s="5">
         <v>101</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I19" s="10">
@@ -1374,11 +1991,11 @@
       <c r="K19" s="5">
         <v>110003</v>
       </c>
-      <c r="L19" s="13" t="s">
+      <c r="L19" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B20" s="7"/>
       <c r="C20" s="5">
         <f t="shared" si="0"/>
@@ -1396,7 +2013,7 @@
       <c r="G20" s="5">
         <v>102</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="10">
@@ -1408,11 +2025,11 @@
       <c r="K20" s="5">
         <v>110003</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L20" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="21" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B21" s="7"/>
       <c r="C21" s="5">
         <f t="shared" si="0"/>
@@ -1430,7 +2047,7 @@
       <c r="G21" s="5">
         <v>103</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="14" t="s">
         <v>39</v>
       </c>
       <c r="I21" s="10">
@@ -1442,11 +2059,11 @@
       <c r="K21" s="5">
         <v>110003</v>
       </c>
-      <c r="L21" s="13" t="s">
+      <c r="L21" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="22" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B22" s="7"/>
       <c r="C22" s="5">
         <f t="shared" si="0"/>
@@ -1464,7 +2081,7 @@
       <c r="G22" s="5">
         <v>201</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I22" s="10">
@@ -1476,11 +2093,11 @@
       <c r="K22" s="5">
         <v>110003</v>
       </c>
-      <c r="L22" s="13" t="s">
+      <c r="L22" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="23" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B23" s="7"/>
       <c r="C23" s="5">
         <f t="shared" si="0"/>
@@ -1498,7 +2115,7 @@
       <c r="G23" s="5">
         <v>202</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I23" s="10">
@@ -1510,11 +2127,11 @@
       <c r="K23" s="5">
         <v>110003</v>
       </c>
-      <c r="L23" s="13" t="s">
+      <c r="L23" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="24" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B24" s="7"/>
       <c r="C24" s="5">
         <f t="shared" si="0"/>
@@ -1532,7 +2149,7 @@
       <c r="G24" s="5">
         <v>203</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="14" t="s">
         <v>41</v>
       </c>
       <c r="I24" s="10">
@@ -1544,11 +2161,11 @@
       <c r="K24" s="5">
         <v>110003</v>
       </c>
-      <c r="L24" s="13" t="s">
+      <c r="L24" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="25" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B25" s="7"/>
       <c r="C25" s="5">
         <f t="shared" si="0"/>
@@ -1566,7 +2183,7 @@
       <c r="G25" s="5">
         <v>101</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="14" t="s">
         <v>42</v>
       </c>
       <c r="I25" s="10">
@@ -1578,11 +2195,11 @@
       <c r="K25" s="5">
         <v>110004</v>
       </c>
-      <c r="L25" s="13" t="s">
+      <c r="L25" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="26" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B26" s="7"/>
       <c r="C26" s="5">
         <f t="shared" si="0"/>
@@ -1600,7 +2217,7 @@
       <c r="G26" s="5">
         <v>102</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="14" t="s">
         <v>42</v>
       </c>
       <c r="I26" s="10">
@@ -1612,11 +2229,11 @@
       <c r="K26" s="5">
         <v>110004</v>
       </c>
-      <c r="L26" s="13" t="s">
+      <c r="L26" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B27" s="7"/>
       <c r="C27" s="5">
         <f t="shared" si="0"/>
@@ -1634,7 +2251,7 @@
       <c r="G27" s="5">
         <v>103</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="14" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="10">
@@ -1646,11 +2263,11 @@
       <c r="K27" s="5">
         <v>110004</v>
       </c>
-      <c r="L27" s="13" t="s">
+      <c r="L27" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="28" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B28" s="7"/>
       <c r="C28" s="5">
         <f t="shared" si="0"/>
@@ -1668,7 +2285,7 @@
       <c r="G28" s="5">
         <v>201</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I28" s="10">
@@ -1680,11 +2297,11 @@
       <c r="K28" s="5">
         <v>110004</v>
       </c>
-      <c r="L28" s="13" t="s">
+      <c r="L28" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="29" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B29" s="7"/>
       <c r="C29" s="5">
         <f t="shared" si="0"/>
@@ -1702,7 +2319,7 @@
       <c r="G29" s="5">
         <v>202</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I29" s="10">
@@ -1714,11 +2331,11 @@
       <c r="K29" s="5">
         <v>110004</v>
       </c>
-      <c r="L29" s="13" t="s">
+      <c r="L29" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="30" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B30" s="7"/>
       <c r="C30" s="5">
         <f t="shared" si="0"/>
@@ -1736,7 +2353,7 @@
       <c r="G30" s="5">
         <v>203</v>
       </c>
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="14" t="s">
         <v>46</v>
       </c>
       <c r="I30" s="10">
@@ -1748,11 +2365,11 @@
       <c r="K30" s="5">
         <v>110004</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="L30" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="31" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B31" s="7"/>
       <c r="C31" s="5">
         <f t="shared" si="0"/>
@@ -1770,10 +2387,10 @@
       <c r="G31" s="5">
         <v>101</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="14" t="s">
+      <c r="I31" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J31" s="8">
@@ -1782,11 +2399,11 @@
       <c r="K31" s="5">
         <v>110005</v>
       </c>
-      <c r="L31" s="13" t="s">
+      <c r="L31" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="32" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B32" s="7"/>
       <c r="C32" s="5">
         <f t="shared" si="0"/>
@@ -1804,10 +2421,10 @@
       <c r="G32" s="5">
         <v>102</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="I32" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J32" s="8">
@@ -1816,11 +2433,11 @@
       <c r="K32" s="5">
         <v>110005</v>
       </c>
-      <c r="L32" s="13" t="s">
+      <c r="L32" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="33" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B33" s="7"/>
       <c r="C33" s="5">
         <f t="shared" si="0"/>
@@ -1838,10 +2455,10 @@
       <c r="G33" s="5">
         <v>103</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="H33" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I33" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J33" s="8">
@@ -1850,11 +2467,11 @@
       <c r="K33" s="5">
         <v>110005</v>
       </c>
-      <c r="L33" s="13" t="s">
+      <c r="L33" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="34" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B34" s="7"/>
       <c r="C34" s="5">
         <f t="shared" si="0"/>
@@ -1872,10 +2489,10 @@
       <c r="G34" s="5">
         <v>201</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="14" t="s">
+      <c r="I34" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J34" s="8">
@@ -1884,11 +2501,11 @@
       <c r="K34" s="5">
         <v>110005</v>
       </c>
-      <c r="L34" s="13" t="s">
+      <c r="L34" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="35" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B35" s="7"/>
       <c r="C35" s="5">
         <f t="shared" si="0"/>
@@ -1906,10 +2523,10 @@
       <c r="G35" s="5">
         <v>202</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="14" t="s">
+      <c r="I35" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J35" s="8">
@@ -1918,11 +2535,11 @@
       <c r="K35" s="5">
         <v>110005</v>
       </c>
-      <c r="L35" s="13" t="s">
+      <c r="L35" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="36" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B36" s="7"/>
       <c r="C36" s="5">
         <f t="shared" si="0"/>
@@ -1940,10 +2557,10 @@
       <c r="G36" s="5">
         <v>203</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I36" s="14" t="s">
+      <c r="I36" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J36" s="8">
@@ -1952,11 +2569,11 @@
       <c r="K36" s="5">
         <v>110005</v>
       </c>
-      <c r="L36" s="13" t="s">
+      <c r="L36" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="37" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B37" s="7"/>
       <c r="C37" s="5">
         <f t="shared" si="0"/>
@@ -1974,10 +2591,10 @@
       <c r="G37" s="5">
         <v>101</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I37" s="14" t="s">
+      <c r="I37" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J37" s="8">
@@ -1986,11 +2603,11 @@
       <c r="K37" s="5">
         <v>110006</v>
       </c>
-      <c r="L37" s="13" t="s">
+      <c r="L37" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="38" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B38" s="7"/>
       <c r="C38" s="5">
         <f t="shared" si="0"/>
@@ -2008,10 +2625,10 @@
       <c r="G38" s="5">
         <v>102</v>
       </c>
-      <c r="H38" s="12" t="s">
+      <c r="H38" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I38" s="14" t="s">
+      <c r="I38" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J38" s="8">
@@ -2020,11 +2637,11 @@
       <c r="K38" s="5">
         <v>110006</v>
       </c>
-      <c r="L38" s="13" t="s">
+      <c r="L38" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="39" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B39" s="7"/>
       <c r="C39" s="5">
         <f t="shared" si="0"/>
@@ -2042,10 +2659,10 @@
       <c r="G39" s="5">
         <v>103</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="H39" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="I39" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="8">
@@ -2054,11 +2671,11 @@
       <c r="K39" s="5">
         <v>110006</v>
       </c>
-      <c r="L39" s="13" t="s">
+      <c r="L39" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="40" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B40" s="7"/>
       <c r="C40" s="5">
         <f t="shared" si="0"/>
@@ -2076,10 +2693,10 @@
       <c r="G40" s="5">
         <v>201</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H40" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I40" s="14" t="s">
+      <c r="I40" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="8">
@@ -2088,11 +2705,11 @@
       <c r="K40" s="5">
         <v>110006</v>
       </c>
-      <c r="L40" s="13" t="s">
+      <c r="L40" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="41" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B41" s="7"/>
       <c r="C41" s="5">
         <f t="shared" si="0"/>
@@ -2110,10 +2727,10 @@
       <c r="G41" s="5">
         <v>202</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="I41" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="8">
@@ -2122,11 +2739,11 @@
       <c r="K41" s="5">
         <v>110006</v>
       </c>
-      <c r="L41" s="13" t="s">
+      <c r="L41" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="42" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B42" s="7"/>
       <c r="C42" s="5">
         <f t="shared" si="0"/>
@@ -2144,10 +2761,10 @@
       <c r="G42" s="5">
         <v>203</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H42" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I42" s="14" t="s">
+      <c r="I42" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J42" s="8">
@@ -2156,18 +2773,18 @@
       <c r="K42" s="5">
         <v>110006</v>
       </c>
-      <c r="L42" s="13" t="s">
+      <c r="L42" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="43" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B43" s="7"/>
       <c r="C43" s="5">
         <f t="shared" si="0"/>
         <v>2701</v>
       </c>
       <c r="D43" s="5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>26</v>
@@ -2178,30 +2795,30 @@
       <c r="G43" s="5">
         <v>101</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="H43" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I43" s="14" t="s">
+      <c r="I43" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J43" s="8">
         <v>2</v>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="12">
         <v>110007</v>
       </c>
-      <c r="L43" s="13" t="s">
+      <c r="L43" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="44" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B44" s="7"/>
       <c r="C44" s="5">
         <f t="shared" si="0"/>
         <v>2702</v>
       </c>
       <c r="D44" s="5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>26</v>
@@ -2212,30 +2829,30 @@
       <c r="G44" s="5">
         <v>102</v>
       </c>
-      <c r="H44" s="12" t="s">
+      <c r="H44" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I44" s="14" t="s">
+      <c r="I44" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J44" s="8">
         <v>2</v>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="12">
         <v>110007</v>
       </c>
-      <c r="L44" s="13" t="s">
+      <c r="L44" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="45" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B45" s="7"/>
       <c r="C45" s="5">
         <f t="shared" si="0"/>
         <v>2703</v>
       </c>
       <c r="D45" s="5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>26</v>
@@ -2246,30 +2863,30 @@
       <c r="G45" s="5">
         <v>103</v>
       </c>
-      <c r="H45" s="12" t="s">
+      <c r="H45" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I45" s="14" t="s">
+      <c r="I45" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J45" s="8">
         <v>2</v>
       </c>
-      <c r="K45" s="16">
+      <c r="K45" s="12">
         <v>110007</v>
       </c>
-      <c r="L45" s="13" t="s">
+      <c r="L45" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="46" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B46" s="7"/>
       <c r="C46" s="5">
         <f t="shared" si="0"/>
         <v>2704</v>
       </c>
       <c r="D46" s="5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>26</v>
@@ -2280,30 +2897,30 @@
       <c r="G46" s="5">
         <v>201</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I46" s="14" t="s">
+      <c r="I46" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J46" s="8">
         <v>2</v>
       </c>
-      <c r="K46" s="16">
+      <c r="K46" s="12">
         <v>110007</v>
       </c>
-      <c r="L46" s="13" t="s">
+      <c r="L46" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="47" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B47" s="7"/>
       <c r="C47" s="5">
         <f t="shared" si="0"/>
         <v>2705</v>
       </c>
       <c r="D47" s="5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>26</v>
@@ -2314,30 +2931,30 @@
       <c r="G47" s="5">
         <v>202</v>
       </c>
-      <c r="H47" s="12" t="s">
+      <c r="H47" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I47" s="14" t="s">
+      <c r="I47" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J47" s="8">
         <v>2</v>
       </c>
-      <c r="K47" s="16">
+      <c r="K47" s="12">
         <v>110007</v>
       </c>
-      <c r="L47" s="13" t="s">
+      <c r="L47" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="48" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B48" s="7"/>
       <c r="C48" s="5">
         <f t="shared" si="0"/>
         <v>2706</v>
       </c>
       <c r="D48" s="5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>26</v>
@@ -2348,23 +2965,23 @@
       <c r="G48" s="5">
         <v>203</v>
       </c>
-      <c r="H48" s="12" t="s">
+      <c r="H48" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I48" s="14" t="s">
+      <c r="I48" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J48" s="8">
         <v>2</v>
       </c>
-      <c r="K48" s="16">
+      <c r="K48" s="12">
         <v>110007</v>
       </c>
-      <c r="L48" s="13" t="s">
+      <c r="L48" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="49" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B49" s="7"/>
       <c r="C49" s="5">
         <v>3001</v>
@@ -2381,7 +2998,7 @@
       <c r="G49" s="5">
         <v>101</v>
       </c>
-      <c r="H49" s="12" t="s">
+      <c r="H49" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I49" s="10">
@@ -2391,11 +3008,11 @@
         <v>3</v>
       </c>
       <c r="K49" s="5"/>
-      <c r="L49" s="15" t="s">
+      <c r="L49" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="50" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B50" s="7"/>
       <c r="C50" s="5">
         <v>3002</v>
@@ -2412,7 +3029,7 @@
       <c r="G50" s="5">
         <v>102</v>
       </c>
-      <c r="H50" s="12" t="s">
+      <c r="H50" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I50" s="10">
@@ -2422,11 +3039,11 @@
         <v>3</v>
       </c>
       <c r="K50" s="5"/>
-      <c r="L50" s="15" t="s">
+      <c r="L50" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="51" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B51" s="7"/>
       <c r="C51" s="5">
         <v>3003</v>
@@ -2443,7 +3060,7 @@
       <c r="G51" s="5">
         <v>103</v>
       </c>
-      <c r="H51" s="12" t="s">
+      <c r="H51" s="14" t="s">
         <v>29</v>
       </c>
       <c r="I51" s="10">
@@ -2453,11 +3070,11 @@
         <v>3</v>
       </c>
       <c r="K51" s="5"/>
-      <c r="L51" s="15" t="s">
+      <c r="L51" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="52" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B52" s="7"/>
       <c r="C52" s="5">
         <v>3004</v>
@@ -2474,7 +3091,7 @@
       <c r="G52" s="5">
         <v>201</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="H52" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I52" s="10">
@@ -2484,11 +3101,11 @@
         <v>3</v>
       </c>
       <c r="K52" s="5"/>
-      <c r="L52" s="15" t="s">
+      <c r="L52" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="53" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B53" s="7"/>
       <c r="C53" s="5">
         <v>3005</v>
@@ -2505,7 +3122,7 @@
       <c r="G53" s="5">
         <v>202</v>
       </c>
-      <c r="H53" s="12" t="s">
+      <c r="H53" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="10">
@@ -2515,11 +3132,11 @@
         <v>3</v>
       </c>
       <c r="K53" s="5"/>
-      <c r="L53" s="15" t="s">
+      <c r="L53" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="54" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B54" s="7"/>
       <c r="C54" s="5">
         <v>3006</v>
@@ -2536,7 +3153,7 @@
       <c r="G54" s="5">
         <v>203</v>
       </c>
-      <c r="H54" s="12" t="s">
+      <c r="H54" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="10">
@@ -2546,11 +3163,11 @@
         <v>3</v>
       </c>
       <c r="K54" s="5"/>
-      <c r="L54" s="15" t="s">
+      <c r="L54" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="55" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B55" s="7"/>
       <c r="C55" s="5">
         <v>3051</v>
@@ -2567,7 +3184,7 @@
       <c r="G55" s="5">
         <v>101</v>
       </c>
-      <c r="H55" s="12" t="s">
+      <c r="H55" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I55" s="10">
@@ -2577,11 +3194,11 @@
         <v>3</v>
       </c>
       <c r="K55" s="5"/>
-      <c r="L55" s="15" t="s">
+      <c r="L55" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="56" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B56" s="7"/>
       <c r="C56" s="5">
         <v>3052</v>
@@ -2598,7 +3215,7 @@
       <c r="G56" s="5">
         <v>102</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="H56" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I56" s="10">
@@ -2608,11 +3225,11 @@
         <v>3</v>
       </c>
       <c r="K56" s="5"/>
-      <c r="L56" s="15" t="s">
+      <c r="L56" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="57" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B57" s="7"/>
       <c r="C57" s="5">
         <v>3053</v>
@@ -2629,7 +3246,7 @@
       <c r="G57" s="5">
         <v>103</v>
       </c>
-      <c r="H57" s="12" t="s">
+      <c r="H57" s="14" t="s">
         <v>34</v>
       </c>
       <c r="I57" s="10">
@@ -2639,11 +3256,11 @@
         <v>3</v>
       </c>
       <c r="K57" s="5"/>
-      <c r="L57" s="15" t="s">
+      <c r="L57" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="58" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B58" s="7"/>
       <c r="C58" s="5">
         <v>3054</v>
@@ -2660,7 +3277,7 @@
       <c r="G58" s="5">
         <v>201</v>
       </c>
-      <c r="H58" s="12" t="s">
+      <c r="H58" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I58" s="10">
@@ -2670,11 +3287,11 @@
         <v>3</v>
       </c>
       <c r="K58" s="5"/>
-      <c r="L58" s="15" t="s">
+      <c r="L58" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="59" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B59" s="7"/>
       <c r="C59" s="5">
         <v>3055</v>
@@ -2691,7 +3308,7 @@
       <c r="G59" s="5">
         <v>202</v>
       </c>
-      <c r="H59" s="12" t="s">
+      <c r="H59" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I59" s="10">
@@ -2701,11 +3318,11 @@
         <v>3</v>
       </c>
       <c r="K59" s="5"/>
-      <c r="L59" s="15" t="s">
+      <c r="L59" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="60" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B60" s="7"/>
       <c r="C60" s="5">
         <v>3056</v>
@@ -2722,7 +3339,7 @@
       <c r="G60" s="5">
         <v>203</v>
       </c>
-      <c r="H60" s="12" t="s">
+      <c r="H60" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I60" s="10">
@@ -2732,11 +3349,11 @@
         <v>3</v>
       </c>
       <c r="K60" s="5"/>
-      <c r="L60" s="15" t="s">
+      <c r="L60" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="61" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B61" s="7"/>
       <c r="C61" s="5">
         <v>5101</v>
@@ -2753,7 +3370,7 @@
       <c r="G61" s="5">
         <v>101</v>
       </c>
-      <c r="H61" s="12" t="s">
+      <c r="H61" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I61" s="5" t="s">
@@ -2767,7 +3384,7 @@
       </c>
       <c r="L61" s="11"/>
     </row>
-    <row r="62" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="62" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B62" s="7"/>
       <c r="C62" s="5">
         <v>5102</v>
@@ -2784,7 +3401,7 @@
       <c r="G62" s="5">
         <v>102</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I62" s="5" t="s">
@@ -2798,7 +3415,7 @@
       </c>
       <c r="L62" s="11"/>
     </row>
-    <row r="63" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="63" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B63" s="7"/>
       <c r="C63" s="5">
         <v>5103</v>
@@ -2815,7 +3432,7 @@
       <c r="G63" s="5">
         <v>103</v>
       </c>
-      <c r="H63" s="12" t="s">
+      <c r="H63" s="14" t="s">
         <v>29</v>
       </c>
       <c r="I63" s="5" t="s">
@@ -2829,7 +3446,7 @@
       </c>
       <c r="L63" s="11"/>
     </row>
-    <row r="64" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="64" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B64" s="7"/>
       <c r="C64" s="5">
         <v>5104</v>
@@ -2846,7 +3463,7 @@
       <c r="G64" s="5">
         <v>201</v>
       </c>
-      <c r="H64" s="12" t="s">
+      <c r="H64" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I64" s="5" t="s">
@@ -2860,7 +3477,7 @@
       </c>
       <c r="L64" s="11"/>
     </row>
-    <row r="65" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="65" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B65" s="7"/>
       <c r="C65" s="5">
         <v>5105</v>
@@ -2877,7 +3494,7 @@
       <c r="G65" s="5">
         <v>202</v>
       </c>
-      <c r="H65" s="12" t="s">
+      <c r="H65" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I65" s="5" t="s">
@@ -2891,7 +3508,7 @@
       </c>
       <c r="L65" s="11"/>
     </row>
-    <row r="66" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="66" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B66" s="7"/>
       <c r="C66" s="5">
         <v>5106</v>
@@ -2908,7 +3525,7 @@
       <c r="G66" s="5">
         <v>203</v>
       </c>
-      <c r="H66" s="12" t="s">
+      <c r="H66" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="5" t="s">
@@ -2922,7 +3539,7 @@
       </c>
       <c r="L66" s="11"/>
     </row>
-    <row r="67" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="67" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B67" s="7"/>
       <c r="C67" s="5">
         <v>5201</v>
@@ -2939,7 +3556,7 @@
       <c r="G67" s="5">
         <v>101</v>
       </c>
-      <c r="H67" s="12" t="s">
+      <c r="H67" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I67" s="10">
@@ -2953,7 +3570,7 @@
       </c>
       <c r="L67" s="11"/>
     </row>
-    <row r="68" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="68" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B68" s="7"/>
       <c r="C68" s="5">
         <v>5202</v>
@@ -2970,7 +3587,7 @@
       <c r="G68" s="5">
         <v>102</v>
       </c>
-      <c r="H68" s="12" t="s">
+      <c r="H68" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I68" s="10">
@@ -2984,7 +3601,7 @@
       </c>
       <c r="L68" s="11"/>
     </row>
-    <row r="69" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="69" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B69" s="7"/>
       <c r="C69" s="5">
         <v>5203</v>
@@ -3001,7 +3618,7 @@
       <c r="G69" s="5">
         <v>103</v>
       </c>
-      <c r="H69" s="12" t="s">
+      <c r="H69" s="14" t="s">
         <v>34</v>
       </c>
       <c r="I69" s="10">
@@ -3015,7 +3632,7 @@
       </c>
       <c r="L69" s="11"/>
     </row>
-    <row r="70" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="70" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B70" s="7"/>
       <c r="C70" s="5">
         <v>5204</v>
@@ -3032,7 +3649,7 @@
       <c r="G70" s="5">
         <v>201</v>
       </c>
-      <c r="H70" s="12" t="s">
+      <c r="H70" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I70" s="10">
@@ -3046,7 +3663,7 @@
       </c>
       <c r="L70" s="11"/>
     </row>
-    <row r="71" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="71" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B71" s="7"/>
       <c r="C71" s="5">
         <v>5205</v>
@@ -3063,7 +3680,7 @@
       <c r="G71" s="5">
         <v>202</v>
       </c>
-      <c r="H71" s="12" t="s">
+      <c r="H71" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I71" s="10">
@@ -3077,7 +3694,7 @@
       </c>
       <c r="L71" s="11"/>
     </row>
-    <row r="72" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="72" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B72" s="7"/>
       <c r="C72" s="5">
         <v>5206</v>
@@ -3094,7 +3711,7 @@
       <c r="G72" s="5">
         <v>203</v>
       </c>
-      <c r="H72" s="12" t="s">
+      <c r="H72" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I72" s="10">
@@ -3108,7 +3725,7 @@
       </c>
       <c r="L72" s="11"/>
     </row>
-    <row r="73" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="73" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B73" s="7"/>
       <c r="C73" s="5">
         <v>5301</v>
@@ -3125,7 +3742,7 @@
       <c r="G73" s="5">
         <v>101</v>
       </c>
-      <c r="H73" s="12" t="s">
+      <c r="H73" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I73" s="10">
@@ -3139,7 +3756,7 @@
       </c>
       <c r="L73" s="11"/>
     </row>
-    <row r="74" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="74" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B74" s="7"/>
       <c r="C74" s="5">
         <v>5302</v>
@@ -3156,7 +3773,7 @@
       <c r="G74" s="5">
         <v>102</v>
       </c>
-      <c r="H74" s="12" t="s">
+      <c r="H74" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I74" s="10">
@@ -3170,7 +3787,7 @@
       </c>
       <c r="L74" s="11"/>
     </row>
-    <row r="75" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="75" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B75" s="7"/>
       <c r="C75" s="5">
         <v>5303</v>
@@ -3187,7 +3804,7 @@
       <c r="G75" s="5">
         <v>103</v>
       </c>
-      <c r="H75" s="12" t="s">
+      <c r="H75" s="14" t="s">
         <v>39</v>
       </c>
       <c r="I75" s="10">
@@ -3201,7 +3818,7 @@
       </c>
       <c r="L75" s="11"/>
     </row>
-    <row r="76" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="76" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B76" s="7"/>
       <c r="C76" s="5">
         <v>5304</v>
@@ -3218,7 +3835,7 @@
       <c r="G76" s="5">
         <v>201</v>
       </c>
-      <c r="H76" s="12" t="s">
+      <c r="H76" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I76" s="10">
@@ -3232,7 +3849,7 @@
       </c>
       <c r="L76" s="11"/>
     </row>
-    <row r="77" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="77" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B77" s="7"/>
       <c r="C77" s="5">
         <v>5305</v>
@@ -3249,7 +3866,7 @@
       <c r="G77" s="5">
         <v>202</v>
       </c>
-      <c r="H77" s="12" t="s">
+      <c r="H77" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I77" s="10">
@@ -3263,7 +3880,7 @@
       </c>
       <c r="L77" s="11"/>
     </row>
-    <row r="78" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="78" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B78" s="7"/>
       <c r="C78" s="5">
         <v>5306</v>
@@ -3280,7 +3897,7 @@
       <c r="G78" s="5">
         <v>203</v>
       </c>
-      <c r="H78" s="12" t="s">
+      <c r="H78" s="14" t="s">
         <v>41</v>
       </c>
       <c r="I78" s="10">
@@ -3294,7 +3911,7 @@
       </c>
       <c r="L78" s="11"/>
     </row>
-    <row r="79" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="79" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B79" s="7"/>
       <c r="C79" s="5">
         <v>5401</v>
@@ -3311,7 +3928,7 @@
       <c r="G79" s="5">
         <v>101</v>
       </c>
-      <c r="H79" s="12" t="s">
+      <c r="H79" s="14" t="s">
         <v>42</v>
       </c>
       <c r="I79" s="10">
@@ -3325,7 +3942,7 @@
       </c>
       <c r="L79" s="11"/>
     </row>
-    <row r="80" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="80" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B80" s="7"/>
       <c r="C80" s="5">
         <v>5402</v>
@@ -3342,7 +3959,7 @@
       <c r="G80" s="5">
         <v>102</v>
       </c>
-      <c r="H80" s="12" t="s">
+      <c r="H80" s="14" t="s">
         <v>42</v>
       </c>
       <c r="I80" s="10">
@@ -3356,7 +3973,7 @@
       </c>
       <c r="L80" s="11"/>
     </row>
-    <row r="81" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="81" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B81" s="7"/>
       <c r="C81" s="5">
         <v>5403</v>
@@ -3373,7 +3990,7 @@
       <c r="G81" s="5">
         <v>103</v>
       </c>
-      <c r="H81" s="12" t="s">
+      <c r="H81" s="14" t="s">
         <v>44</v>
       </c>
       <c r="I81" s="10">
@@ -3387,7 +4004,7 @@
       </c>
       <c r="L81" s="11"/>
     </row>
-    <row r="82" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="82" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B82" s="7"/>
       <c r="C82" s="5">
         <v>5404</v>
@@ -3404,7 +4021,7 @@
       <c r="G82" s="5">
         <v>201</v>
       </c>
-      <c r="H82" s="12" t="s">
+      <c r="H82" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I82" s="10">
@@ -3418,7 +4035,7 @@
       </c>
       <c r="L82" s="11"/>
     </row>
-    <row r="83" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="83" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B83" s="7"/>
       <c r="C83" s="5">
         <v>5405</v>
@@ -3435,7 +4052,7 @@
       <c r="G83" s="5">
         <v>202</v>
       </c>
-      <c r="H83" s="12" t="s">
+      <c r="H83" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I83" s="10">
@@ -3449,7 +4066,7 @@
       </c>
       <c r="L83" s="11"/>
     </row>
-    <row r="84" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="84" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B84" s="7"/>
       <c r="C84" s="5">
         <v>5406</v>
@@ -3466,7 +4083,7 @@
       <c r="G84" s="5">
         <v>203</v>
       </c>
-      <c r="H84" s="12" t="s">
+      <c r="H84" s="14" t="s">
         <v>46</v>
       </c>
       <c r="I84" s="10">
@@ -3480,7 +4097,7 @@
       </c>
       <c r="L84" s="11"/>
     </row>
-    <row r="85" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="85" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B85" s="7"/>
       <c r="C85" s="5">
         <v>5001</v>
@@ -3497,7 +4114,7 @@
       <c r="G85" s="5">
         <v>203</v>
       </c>
-      <c r="H85" s="12" t="s">
+      <c r="H85" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I85" s="10">
@@ -3507,11 +4124,11 @@
         <v>5</v>
       </c>
       <c r="K85" s="5"/>
-      <c r="L85" s="15" t="s">
+      <c r="L85" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="86" spans="2:12" ht="20.100000000000001" customHeight="1">
+    <row r="86" ht="20.1" customHeight="1" spans="2:12">
       <c r="C86" s="5">
         <v>6001</v>
       </c>
@@ -3527,7 +4144,7 @@
       <c r="G86" s="3">
         <v>203</v>
       </c>
-      <c r="H86" s="12" t="s">
+      <c r="H86" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I86" s="10">
@@ -3537,7 +4154,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="87" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B87" s="7"/>
       <c r="C87" s="5">
         <v>7001</v>
@@ -3564,7 +4181,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="9"/>
     </row>
-    <row r="88" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="88" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B88" s="7"/>
       <c r="C88" s="5">
         <v>8001</v>
@@ -3591,7 +4208,7 @@
       <c r="K88" s="5"/>
       <c r="L88" s="9"/>
     </row>
-    <row r="89" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="89" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B89" s="7"/>
       <c r="C89" s="5">
         <v>9001</v>
@@ -3608,7 +4225,7 @@
       <c r="G89" s="5">
         <v>0</v>
       </c>
-      <c r="H89" s="12" t="s">
+      <c r="H89" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I89" s="5" t="s">
@@ -3618,11 +4235,11 @@
         <v>9</v>
       </c>
       <c r="K89" s="5"/>
-      <c r="L89" s="13" t="s">
+      <c r="L89" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="90" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="90" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B90" s="7"/>
       <c r="C90" s="5">
         <v>10001</v>
@@ -3639,7 +4256,7 @@
       <c r="G90" s="5">
         <v>0</v>
       </c>
-      <c r="H90" s="12" t="s">
+      <c r="H90" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I90" s="5" t="s">
@@ -3649,11 +4266,11 @@
         <v>10</v>
       </c>
       <c r="K90" s="5"/>
-      <c r="L90" s="13" t="s">
+      <c r="L90" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="91" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="91" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B91" s="7"/>
       <c r="C91" s="5">
         <v>11001</v>
@@ -3670,7 +4287,7 @@
       <c r="G91" s="5">
         <v>0</v>
       </c>
-      <c r="H91" s="12" t="s">
+      <c r="H91" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I91" s="5" t="s">
@@ -3680,14 +4297,14 @@
         <v>11</v>
       </c>
       <c r="K91" s="5"/>
-      <c r="L91" s="13" t="s">
+      <c r="L91" s="15" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/RobotConfig.xlsx
+++ b/Excel/RobotConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA528769-0984-48FB-AE9D-482DDF4493B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="809"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RobotConfig" sheetId="1" r:id="rId1"/>
@@ -27,19 +33,20 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="I3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -48,6 +55,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -55,13 +63,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="1">
+    <comment ref="J3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -70,6 +79,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -86,13 +96,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1">
+    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -101,6 +112,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -108,13 +120,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -123,6 +136,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -135,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="66">
   <si>
     <t>cs</t>
   </si>
@@ -327,19 +341,19 @@
   </si>
   <si>
     <t>宝藏之地机器人</t>
+  </si>
+  <si>
+    <t>58.35,28.77,-128.42</t>
+  </si>
+  <si>
+    <t>190.75,29.92,-64.15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,6 +365,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -358,183 +373,68 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -553,194 +453,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -761,363 +475,77 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 6" xfId="50"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1375,12 +803,12 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -1398,7 +826,7 @@
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1414,7 +842,7 @@
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1430,7 +858,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
@@ -1464,7 +892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
@@ -1498,7 +926,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
@@ -1532,7 +960,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B6" s="7"/>
       <c r="C6" s="5">
         <v>1001</v>
@@ -1559,7 +987,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="9"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="7" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B7" s="7"/>
       <c r="C7" s="5">
         <v>2101</v>
@@ -1576,7 +1004,7 @@
       <c r="G7" s="5">
         <v>101</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="13" t="s">
         <v>27</v>
       </c>
       <c r="I7" s="10">
@@ -1588,11 +1016,11 @@
       <c r="K7" s="5">
         <v>110001</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="8" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B8" s="7"/>
       <c r="C8" s="5">
         <v>2102</v>
@@ -1609,7 +1037,7 @@
       <c r="G8" s="5">
         <v>102</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="13" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="10">
@@ -1621,11 +1049,11 @@
       <c r="K8" s="5">
         <v>110001</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="9" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B9" s="7"/>
       <c r="C9" s="5">
         <v>2103</v>
@@ -1642,7 +1070,7 @@
       <c r="G9" s="5">
         <v>103</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I9" s="10">
@@ -1654,11 +1082,11 @@
       <c r="K9" s="5">
         <v>110001</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="10" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B10" s="7"/>
       <c r="C10" s="5">
         <v>2104</v>
@@ -1675,7 +1103,7 @@
       <c r="G10" s="5">
         <v>201</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="13" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="10">
@@ -1687,11 +1115,11 @@
       <c r="K10" s="5">
         <v>110001</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="11" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B11" s="7"/>
       <c r="C11" s="5">
         <v>2105</v>
@@ -1708,7 +1136,7 @@
       <c r="G11" s="5">
         <v>202</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="13" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="10">
@@ -1720,11 +1148,11 @@
       <c r="K11" s="5">
         <v>110001</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="12" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B12" s="7"/>
       <c r="C12" s="5">
         <v>2106</v>
@@ -1741,7 +1169,7 @@
       <c r="G12" s="5">
         <v>203</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="10">
@@ -1753,11 +1181,11 @@
       <c r="K12" s="5">
         <v>110001</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="13" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B13" s="7"/>
       <c r="C13" s="5">
         <f>C7+100</f>
@@ -1775,7 +1203,7 @@
       <c r="G13" s="5">
         <v>101</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="13" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="10">
@@ -1787,11 +1215,11 @@
       <c r="K13" s="5">
         <v>110002</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="14" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B14" s="7"/>
       <c r="C14" s="5">
         <f t="shared" ref="C14:C48" si="0">C8+100</f>
@@ -1809,7 +1237,7 @@
       <c r="G14" s="5">
         <v>102</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="13" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="10">
@@ -1821,11 +1249,11 @@
       <c r="K14" s="5">
         <v>110002</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="L14" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="15" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="7"/>
       <c r="C15" s="5">
         <f t="shared" si="0"/>
@@ -1843,7 +1271,7 @@
       <c r="G15" s="5">
         <v>103</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="13" t="s">
         <v>34</v>
       </c>
       <c r="I15" s="10">
@@ -1855,11 +1283,11 @@
       <c r="K15" s="5">
         <v>110002</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="L15" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
+    <row r="16" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B16" s="7"/>
       <c r="C16" s="5">
         <f t="shared" si="0"/>
@@ -1877,7 +1305,7 @@
       <c r="G16" s="5">
         <v>201</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="10">
@@ -1889,11 +1317,11 @@
       <c r="K16" s="5">
         <v>110002</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="L16" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="17" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="7"/>
       <c r="C17" s="5">
         <f t="shared" si="0"/>
@@ -1911,7 +1339,7 @@
       <c r="G17" s="5">
         <v>202</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="10">
@@ -1923,11 +1351,11 @@
       <c r="K17" s="5">
         <v>110002</v>
       </c>
-      <c r="L17" s="15" t="s">
+      <c r="L17" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="18" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="7"/>
       <c r="C18" s="5">
         <f t="shared" si="0"/>
@@ -1945,7 +1373,7 @@
       <c r="G18" s="5">
         <v>203</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="13" t="s">
         <v>36</v>
       </c>
       <c r="I18" s="10">
@@ -1957,11 +1385,11 @@
       <c r="K18" s="5">
         <v>110002</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L18" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="19" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="7"/>
       <c r="C19" s="5">
         <f t="shared" si="0"/>
@@ -1979,7 +1407,7 @@
       <c r="G19" s="5">
         <v>101</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I19" s="10">
@@ -1991,11 +1419,11 @@
       <c r="K19" s="5">
         <v>110003</v>
       </c>
-      <c r="L19" s="15" t="s">
+      <c r="L19" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="20" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="7"/>
       <c r="C20" s="5">
         <f t="shared" si="0"/>
@@ -2013,7 +1441,7 @@
       <c r="G20" s="5">
         <v>102</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="10">
@@ -2025,11 +1453,11 @@
       <c r="K20" s="5">
         <v>110003</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="L20" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="21" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="7"/>
       <c r="C21" s="5">
         <f t="shared" si="0"/>
@@ -2047,7 +1475,7 @@
       <c r="G21" s="5">
         <v>103</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I21" s="10">
@@ -2059,11 +1487,11 @@
       <c r="K21" s="5">
         <v>110003</v>
       </c>
-      <c r="L21" s="15" t="s">
+      <c r="L21" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="22" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B22" s="7"/>
       <c r="C22" s="5">
         <f t="shared" si="0"/>
@@ -2081,7 +1509,7 @@
       <c r="G22" s="5">
         <v>201</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="13" t="s">
         <v>40</v>
       </c>
       <c r="I22" s="10">
@@ -2093,11 +1521,11 @@
       <c r="K22" s="5">
         <v>110003</v>
       </c>
-      <c r="L22" s="15" t="s">
+      <c r="L22" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="23" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="7"/>
       <c r="C23" s="5">
         <f t="shared" si="0"/>
@@ -2115,7 +1543,7 @@
       <c r="G23" s="5">
         <v>202</v>
       </c>
-      <c r="H23" s="14" t="s">
+      <c r="H23" s="13" t="s">
         <v>40</v>
       </c>
       <c r="I23" s="10">
@@ -2127,11 +1555,11 @@
       <c r="K23" s="5">
         <v>110003</v>
       </c>
-      <c r="L23" s="15" t="s">
+      <c r="L23" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="24" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="7"/>
       <c r="C24" s="5">
         <f t="shared" si="0"/>
@@ -2149,7 +1577,7 @@
       <c r="G24" s="5">
         <v>203</v>
       </c>
-      <c r="H24" s="14" t="s">
+      <c r="H24" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I24" s="10">
@@ -2161,11 +1589,11 @@
       <c r="K24" s="5">
         <v>110003</v>
       </c>
-      <c r="L24" s="15" t="s">
+      <c r="L24" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="25" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B25" s="7"/>
       <c r="C25" s="5">
         <f t="shared" si="0"/>
@@ -2183,7 +1611,7 @@
       <c r="G25" s="5">
         <v>101</v>
       </c>
-      <c r="H25" s="14" t="s">
+      <c r="H25" s="13" t="s">
         <v>42</v>
       </c>
       <c r="I25" s="10">
@@ -2195,11 +1623,11 @@
       <c r="K25" s="5">
         <v>110004</v>
       </c>
-      <c r="L25" s="15" t="s">
+      <c r="L25" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="26" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B26" s="7"/>
       <c r="C26" s="5">
         <f t="shared" si="0"/>
@@ -2217,7 +1645,7 @@
       <c r="G26" s="5">
         <v>102</v>
       </c>
-      <c r="H26" s="14" t="s">
+      <c r="H26" s="13" t="s">
         <v>42</v>
       </c>
       <c r="I26" s="10">
@@ -2229,11 +1657,11 @@
       <c r="K26" s="5">
         <v>110004</v>
       </c>
-      <c r="L26" s="15" t="s">
+      <c r="L26" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="27" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B27" s="7"/>
       <c r="C27" s="5">
         <f t="shared" si="0"/>
@@ -2251,7 +1679,7 @@
       <c r="G27" s="5">
         <v>103</v>
       </c>
-      <c r="H27" s="14" t="s">
+      <c r="H27" s="13" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="10">
@@ -2263,11 +1691,11 @@
       <c r="K27" s="5">
         <v>110004</v>
       </c>
-      <c r="L27" s="15" t="s">
+      <c r="L27" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="28" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B28" s="7"/>
       <c r="C28" s="5">
         <f t="shared" si="0"/>
@@ -2285,7 +1713,7 @@
       <c r="G28" s="5">
         <v>201</v>
       </c>
-      <c r="H28" s="14" t="s">
+      <c r="H28" s="13" t="s">
         <v>45</v>
       </c>
       <c r="I28" s="10">
@@ -2297,11 +1725,11 @@
       <c r="K28" s="5">
         <v>110004</v>
       </c>
-      <c r="L28" s="15" t="s">
+      <c r="L28" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="29" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B29" s="7"/>
       <c r="C29" s="5">
         <f t="shared" si="0"/>
@@ -2319,7 +1747,7 @@
       <c r="G29" s="5">
         <v>202</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="H29" s="13" t="s">
         <v>45</v>
       </c>
       <c r="I29" s="10">
@@ -2331,11 +1759,11 @@
       <c r="K29" s="5">
         <v>110004</v>
       </c>
-      <c r="L29" s="15" t="s">
+      <c r="L29" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="30" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B30" s="7"/>
       <c r="C30" s="5">
         <f t="shared" si="0"/>
@@ -2353,7 +1781,7 @@
       <c r="G30" s="5">
         <v>203</v>
       </c>
-      <c r="H30" s="14" t="s">
+      <c r="H30" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I30" s="10">
@@ -2365,11 +1793,11 @@
       <c r="K30" s="5">
         <v>110004</v>
       </c>
-      <c r="L30" s="15" t="s">
+      <c r="L30" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="31" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B31" s="7"/>
       <c r="C31" s="5">
         <f t="shared" si="0"/>
@@ -2387,10 +1815,10 @@
       <c r="G31" s="5">
         <v>101</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="H31" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="16" t="s">
+      <c r="I31" s="15" t="s">
         <v>47</v>
       </c>
       <c r="J31" s="8">
@@ -2399,11 +1827,11 @@
       <c r="K31" s="5">
         <v>110005</v>
       </c>
-      <c r="L31" s="15" t="s">
+      <c r="L31" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="32" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B32" s="7"/>
       <c r="C32" s="5">
         <f t="shared" si="0"/>
@@ -2421,10 +1849,10 @@
       <c r="G32" s="5">
         <v>102</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="H32" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="15" t="s">
         <v>47</v>
       </c>
       <c r="J32" s="8">
@@ -2433,11 +1861,11 @@
       <c r="K32" s="5">
         <v>110005</v>
       </c>
-      <c r="L32" s="15" t="s">
+      <c r="L32" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="33" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B33" s="7"/>
       <c r="C33" s="5">
         <f t="shared" si="0"/>
@@ -2455,10 +1883,10 @@
       <c r="G33" s="5">
         <v>103</v>
       </c>
-      <c r="H33" s="14" t="s">
+      <c r="H33" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I33" s="15" t="s">
         <v>47</v>
       </c>
       <c r="J33" s="8">
@@ -2467,11 +1895,11 @@
       <c r="K33" s="5">
         <v>110005</v>
       </c>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="34" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B34" s="7"/>
       <c r="C34" s="5">
         <f t="shared" si="0"/>
@@ -2489,10 +1917,10 @@
       <c r="G34" s="5">
         <v>201</v>
       </c>
-      <c r="H34" s="14" t="s">
+      <c r="H34" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="16" t="s">
+      <c r="I34" s="15" t="s">
         <v>47</v>
       </c>
       <c r="J34" s="8">
@@ -2501,11 +1929,11 @@
       <c r="K34" s="5">
         <v>110005</v>
       </c>
-      <c r="L34" s="15" t="s">
+      <c r="L34" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="35" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B35" s="7"/>
       <c r="C35" s="5">
         <f t="shared" si="0"/>
@@ -2523,10 +1951,10 @@
       <c r="G35" s="5">
         <v>202</v>
       </c>
-      <c r="H35" s="14" t="s">
+      <c r="H35" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I35" s="15" t="s">
         <v>47</v>
       </c>
       <c r="J35" s="8">
@@ -2535,11 +1963,11 @@
       <c r="K35" s="5">
         <v>110005</v>
       </c>
-      <c r="L35" s="15" t="s">
+      <c r="L35" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="36" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B36" s="7"/>
       <c r="C36" s="5">
         <f t="shared" si="0"/>
@@ -2557,10 +1985,10 @@
       <c r="G36" s="5">
         <v>203</v>
       </c>
-      <c r="H36" s="14" t="s">
+      <c r="H36" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="I36" s="16" t="s">
+      <c r="I36" s="15" t="s">
         <v>47</v>
       </c>
       <c r="J36" s="8">
@@ -2569,11 +1997,11 @@
       <c r="K36" s="5">
         <v>110005</v>
       </c>
-      <c r="L36" s="15" t="s">
+      <c r="L36" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="37" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B37" s="7"/>
       <c r="C37" s="5">
         <f t="shared" si="0"/>
@@ -2591,10 +2019,10 @@
       <c r="G37" s="5">
         <v>101</v>
       </c>
-      <c r="H37" s="14" t="s">
+      <c r="H37" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I37" s="16" t="s">
+      <c r="I37" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J37" s="8">
@@ -2603,11 +2031,11 @@
       <c r="K37" s="5">
         <v>110006</v>
       </c>
-      <c r="L37" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L37" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B38" s="7"/>
       <c r="C38" s="5">
         <f t="shared" si="0"/>
@@ -2625,10 +2053,10 @@
       <c r="G38" s="5">
         <v>102</v>
       </c>
-      <c r="H38" s="14" t="s">
+      <c r="H38" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I38" s="16" t="s">
+      <c r="I38" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J38" s="8">
@@ -2637,11 +2065,11 @@
       <c r="K38" s="5">
         <v>110006</v>
       </c>
-      <c r="L38" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L38" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B39" s="7"/>
       <c r="C39" s="5">
         <f t="shared" si="0"/>
@@ -2659,10 +2087,10 @@
       <c r="G39" s="5">
         <v>103</v>
       </c>
-      <c r="H39" s="14" t="s">
+      <c r="H39" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="16" t="s">
+      <c r="I39" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="8">
@@ -2671,11 +2099,11 @@
       <c r="K39" s="5">
         <v>110006</v>
       </c>
-      <c r="L39" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L39" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B40" s="7"/>
       <c r="C40" s="5">
         <f t="shared" si="0"/>
@@ -2693,10 +2121,10 @@
       <c r="G40" s="5">
         <v>201</v>
       </c>
-      <c r="H40" s="14" t="s">
+      <c r="H40" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I40" s="16" t="s">
+      <c r="I40" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="8">
@@ -2705,11 +2133,11 @@
       <c r="K40" s="5">
         <v>110006</v>
       </c>
-      <c r="L40" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L40" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B41" s="7"/>
       <c r="C41" s="5">
         <f t="shared" si="0"/>
@@ -2727,10 +2155,10 @@
       <c r="G41" s="5">
         <v>202</v>
       </c>
-      <c r="H41" s="14" t="s">
+      <c r="H41" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I41" s="16" t="s">
+      <c r="I41" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="8">
@@ -2739,11 +2167,11 @@
       <c r="K41" s="5">
         <v>110006</v>
       </c>
-      <c r="L41" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L41" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B42" s="7"/>
       <c r="C42" s="5">
         <f t="shared" si="0"/>
@@ -2761,10 +2189,10 @@
       <c r="G42" s="5">
         <v>203</v>
       </c>
-      <c r="H42" s="14" t="s">
+      <c r="H42" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="I42" s="16" t="s">
+      <c r="I42" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J42" s="8">
@@ -2773,11 +2201,11 @@
       <c r="K42" s="5">
         <v>110006</v>
       </c>
-      <c r="L42" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L42" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B43" s="7"/>
       <c r="C43" s="5">
         <f t="shared" si="0"/>
@@ -2795,10 +2223,10 @@
       <c r="G43" s="5">
         <v>101</v>
       </c>
-      <c r="H43" s="14" t="s">
+      <c r="H43" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I43" s="16" t="s">
+      <c r="I43" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J43" s="8">
@@ -2807,11 +2235,11 @@
       <c r="K43" s="12">
         <v>110007</v>
       </c>
-      <c r="L43" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L43" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B44" s="7"/>
       <c r="C44" s="5">
         <f t="shared" si="0"/>
@@ -2829,10 +2257,10 @@
       <c r="G44" s="5">
         <v>102</v>
       </c>
-      <c r="H44" s="14" t="s">
+      <c r="H44" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I44" s="16" t="s">
+      <c r="I44" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J44" s="8">
@@ -2841,11 +2269,11 @@
       <c r="K44" s="12">
         <v>110007</v>
       </c>
-      <c r="L44" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L44" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B45" s="7"/>
       <c r="C45" s="5">
         <f t="shared" si="0"/>
@@ -2863,10 +2291,10 @@
       <c r="G45" s="5">
         <v>103</v>
       </c>
-      <c r="H45" s="14" t="s">
+      <c r="H45" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="I45" s="16" t="s">
+      <c r="I45" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J45" s="8">
@@ -2875,11 +2303,11 @@
       <c r="K45" s="12">
         <v>110007</v>
       </c>
-      <c r="L45" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L45" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B46" s="7"/>
       <c r="C46" s="5">
         <f t="shared" si="0"/>
@@ -2897,10 +2325,10 @@
       <c r="G46" s="5">
         <v>201</v>
       </c>
-      <c r="H46" s="14" t="s">
+      <c r="H46" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I46" s="16" t="s">
+      <c r="I46" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J46" s="8">
@@ -2909,11 +2337,11 @@
       <c r="K46" s="12">
         <v>110007</v>
       </c>
-      <c r="L46" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L46" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B47" s="7"/>
       <c r="C47" s="5">
         <f t="shared" si="0"/>
@@ -2931,10 +2359,10 @@
       <c r="G47" s="5">
         <v>202</v>
       </c>
-      <c r="H47" s="14" t="s">
+      <c r="H47" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I47" s="16" t="s">
+      <c r="I47" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J47" s="8">
@@ -2943,11 +2371,11 @@
       <c r="K47" s="12">
         <v>110007</v>
       </c>
-      <c r="L47" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L47" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B48" s="7"/>
       <c r="C48" s="5">
         <f t="shared" si="0"/>
@@ -2965,10 +2393,10 @@
       <c r="G48" s="5">
         <v>203</v>
       </c>
-      <c r="H48" s="14" t="s">
+      <c r="H48" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="I48" s="16" t="s">
+      <c r="I48" s="15" t="s">
         <v>49</v>
       </c>
       <c r="J48" s="8">
@@ -2977,11 +2405,11 @@
       <c r="K48" s="12">
         <v>110007</v>
       </c>
-      <c r="L48" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="L48" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B49" s="7"/>
       <c r="C49" s="5">
         <v>3001</v>
@@ -2998,7 +2426,7 @@
       <c r="G49" s="5">
         <v>101</v>
       </c>
-      <c r="H49" s="14" t="s">
+      <c r="H49" s="13" t="s">
         <v>27</v>
       </c>
       <c r="I49" s="10">
@@ -3008,11 +2436,11 @@
         <v>3</v>
       </c>
       <c r="K49" s="5"/>
-      <c r="L49" s="17" t="s">
+      <c r="L49" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="50" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B50" s="7"/>
       <c r="C50" s="5">
         <v>3002</v>
@@ -3029,7 +2457,7 @@
       <c r="G50" s="5">
         <v>102</v>
       </c>
-      <c r="H50" s="14" t="s">
+      <c r="H50" s="13" t="s">
         <v>27</v>
       </c>
       <c r="I50" s="10">
@@ -3039,11 +2467,11 @@
         <v>3</v>
       </c>
       <c r="K50" s="5"/>
-      <c r="L50" s="17" t="s">
+      <c r="L50" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="51" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B51" s="7"/>
       <c r="C51" s="5">
         <v>3003</v>
@@ -3060,7 +2488,7 @@
       <c r="G51" s="5">
         <v>103</v>
       </c>
-      <c r="H51" s="14" t="s">
+      <c r="H51" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I51" s="10">
@@ -3070,11 +2498,11 @@
         <v>3</v>
       </c>
       <c r="K51" s="5"/>
-      <c r="L51" s="17" t="s">
+      <c r="L51" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="52" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B52" s="7"/>
       <c r="C52" s="5">
         <v>3004</v>
@@ -3091,7 +2519,7 @@
       <c r="G52" s="5">
         <v>201</v>
       </c>
-      <c r="H52" s="14" t="s">
+      <c r="H52" s="13" t="s">
         <v>30</v>
       </c>
       <c r="I52" s="10">
@@ -3101,11 +2529,11 @@
         <v>3</v>
       </c>
       <c r="K52" s="5"/>
-      <c r="L52" s="17" t="s">
+      <c r="L52" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="53" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B53" s="7"/>
       <c r="C53" s="5">
         <v>3005</v>
@@ -3122,7 +2550,7 @@
       <c r="G53" s="5">
         <v>202</v>
       </c>
-      <c r="H53" s="14" t="s">
+      <c r="H53" s="13" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="10">
@@ -3132,11 +2560,11 @@
         <v>3</v>
       </c>
       <c r="K53" s="5"/>
-      <c r="L53" s="17" t="s">
+      <c r="L53" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="54" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B54" s="7"/>
       <c r="C54" s="5">
         <v>3006</v>
@@ -3153,7 +2581,7 @@
       <c r="G54" s="5">
         <v>203</v>
       </c>
-      <c r="H54" s="14" t="s">
+      <c r="H54" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="10">
@@ -3163,11 +2591,11 @@
         <v>3</v>
       </c>
       <c r="K54" s="5"/>
-      <c r="L54" s="17" t="s">
+      <c r="L54" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="55" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B55" s="7"/>
       <c r="C55" s="5">
         <v>3051</v>
@@ -3184,7 +2612,7 @@
       <c r="G55" s="5">
         <v>101</v>
       </c>
-      <c r="H55" s="14" t="s">
+      <c r="H55" s="13" t="s">
         <v>32</v>
       </c>
       <c r="I55" s="10">
@@ -3194,11 +2622,11 @@
         <v>3</v>
       </c>
       <c r="K55" s="5"/>
-      <c r="L55" s="17" t="s">
+      <c r="L55" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="56" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B56" s="7"/>
       <c r="C56" s="5">
         <v>3052</v>
@@ -3215,7 +2643,7 @@
       <c r="G56" s="5">
         <v>102</v>
       </c>
-      <c r="H56" s="14" t="s">
+      <c r="H56" s="13" t="s">
         <v>32</v>
       </c>
       <c r="I56" s="10">
@@ -3225,11 +2653,11 @@
         <v>3</v>
       </c>
       <c r="K56" s="5"/>
-      <c r="L56" s="17" t="s">
+      <c r="L56" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="57" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B57" s="7"/>
       <c r="C57" s="5">
         <v>3053</v>
@@ -3246,7 +2674,7 @@
       <c r="G57" s="5">
         <v>103</v>
       </c>
-      <c r="H57" s="14" t="s">
+      <c r="H57" s="13" t="s">
         <v>34</v>
       </c>
       <c r="I57" s="10">
@@ -3256,11 +2684,11 @@
         <v>3</v>
       </c>
       <c r="K57" s="5"/>
-      <c r="L57" s="17" t="s">
+      <c r="L57" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="58" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B58" s="7"/>
       <c r="C58" s="5">
         <v>3054</v>
@@ -3277,7 +2705,7 @@
       <c r="G58" s="5">
         <v>201</v>
       </c>
-      <c r="H58" s="14" t="s">
+      <c r="H58" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I58" s="10">
@@ -3287,11 +2715,11 @@
         <v>3</v>
       </c>
       <c r="K58" s="5"/>
-      <c r="L58" s="17" t="s">
+      <c r="L58" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="59" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B59" s="7"/>
       <c r="C59" s="5">
         <v>3055</v>
@@ -3308,7 +2736,7 @@
       <c r="G59" s="5">
         <v>202</v>
       </c>
-      <c r="H59" s="14" t="s">
+      <c r="H59" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I59" s="10">
@@ -3318,11 +2746,11 @@
         <v>3</v>
       </c>
       <c r="K59" s="5"/>
-      <c r="L59" s="17" t="s">
+      <c r="L59" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="60" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B60" s="7"/>
       <c r="C60" s="5">
         <v>3056</v>
@@ -3339,7 +2767,7 @@
       <c r="G60" s="5">
         <v>203</v>
       </c>
-      <c r="H60" s="14" t="s">
+      <c r="H60" s="13" t="s">
         <v>36</v>
       </c>
       <c r="I60" s="10">
@@ -3349,11 +2777,11 @@
         <v>3</v>
       </c>
       <c r="K60" s="5"/>
-      <c r="L60" s="17" t="s">
+      <c r="L60" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="61" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B61" s="7"/>
       <c r="C61" s="5">
         <v>5101</v>
@@ -3370,7 +2798,7 @@
       <c r="G61" s="5">
         <v>101</v>
       </c>
-      <c r="H61" s="14" t="s">
+      <c r="H61" s="13" t="s">
         <v>27</v>
       </c>
       <c r="I61" s="5" t="s">
@@ -3384,7 +2812,7 @@
       </c>
       <c r="L61" s="11"/>
     </row>
-    <row r="62" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="62" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B62" s="7"/>
       <c r="C62" s="5">
         <v>5102</v>
@@ -3401,7 +2829,7 @@
       <c r="G62" s="5">
         <v>102</v>
       </c>
-      <c r="H62" s="14" t="s">
+      <c r="H62" s="13" t="s">
         <v>27</v>
       </c>
       <c r="I62" s="5" t="s">
@@ -3415,7 +2843,7 @@
       </c>
       <c r="L62" s="11"/>
     </row>
-    <row r="63" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="63" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B63" s="7"/>
       <c r="C63" s="5">
         <v>5103</v>
@@ -3432,7 +2860,7 @@
       <c r="G63" s="5">
         <v>103</v>
       </c>
-      <c r="H63" s="14" t="s">
+      <c r="H63" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I63" s="5" t="s">
@@ -3446,7 +2874,7 @@
       </c>
       <c r="L63" s="11"/>
     </row>
-    <row r="64" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="64" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B64" s="7"/>
       <c r="C64" s="5">
         <v>5104</v>
@@ -3463,7 +2891,7 @@
       <c r="G64" s="5">
         <v>201</v>
       </c>
-      <c r="H64" s="14" t="s">
+      <c r="H64" s="13" t="s">
         <v>30</v>
       </c>
       <c r="I64" s="5" t="s">
@@ -3477,7 +2905,7 @@
       </c>
       <c r="L64" s="11"/>
     </row>
-    <row r="65" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="65" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B65" s="7"/>
       <c r="C65" s="5">
         <v>5105</v>
@@ -3494,7 +2922,7 @@
       <c r="G65" s="5">
         <v>202</v>
       </c>
-      <c r="H65" s="14" t="s">
+      <c r="H65" s="13" t="s">
         <v>30</v>
       </c>
       <c r="I65" s="5" t="s">
@@ -3508,7 +2936,7 @@
       </c>
       <c r="L65" s="11"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="66" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B66" s="7"/>
       <c r="C66" s="5">
         <v>5106</v>
@@ -3525,7 +2953,7 @@
       <c r="G66" s="5">
         <v>203</v>
       </c>
-      <c r="H66" s="14" t="s">
+      <c r="H66" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="5" t="s">
@@ -3539,7 +2967,7 @@
       </c>
       <c r="L66" s="11"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="67" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B67" s="7"/>
       <c r="C67" s="5">
         <v>5201</v>
@@ -3556,7 +2984,7 @@
       <c r="G67" s="5">
         <v>101</v>
       </c>
-      <c r="H67" s="14" t="s">
+      <c r="H67" s="13" t="s">
         <v>32</v>
       </c>
       <c r="I67" s="10">
@@ -3570,7 +2998,7 @@
       </c>
       <c r="L67" s="11"/>
     </row>
-    <row r="68" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="68" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B68" s="7"/>
       <c r="C68" s="5">
         <v>5202</v>
@@ -3587,7 +3015,7 @@
       <c r="G68" s="5">
         <v>102</v>
       </c>
-      <c r="H68" s="14" t="s">
+      <c r="H68" s="13" t="s">
         <v>32</v>
       </c>
       <c r="I68" s="10">
@@ -3601,7 +3029,7 @@
       </c>
       <c r="L68" s="11"/>
     </row>
-    <row r="69" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="69" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B69" s="7"/>
       <c r="C69" s="5">
         <v>5203</v>
@@ -3618,7 +3046,7 @@
       <c r="G69" s="5">
         <v>103</v>
       </c>
-      <c r="H69" s="14" t="s">
+      <c r="H69" s="13" t="s">
         <v>34</v>
       </c>
       <c r="I69" s="10">
@@ -3632,7 +3060,7 @@
       </c>
       <c r="L69" s="11"/>
     </row>
-    <row r="70" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="70" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B70" s="7"/>
       <c r="C70" s="5">
         <v>5204</v>
@@ -3649,7 +3077,7 @@
       <c r="G70" s="5">
         <v>201</v>
       </c>
-      <c r="H70" s="14" t="s">
+      <c r="H70" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I70" s="10">
@@ -3663,7 +3091,7 @@
       </c>
       <c r="L70" s="11"/>
     </row>
-    <row r="71" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="71" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B71" s="7"/>
       <c r="C71" s="5">
         <v>5205</v>
@@ -3680,7 +3108,7 @@
       <c r="G71" s="5">
         <v>202</v>
       </c>
-      <c r="H71" s="14" t="s">
+      <c r="H71" s="13" t="s">
         <v>35</v>
       </c>
       <c r="I71" s="10">
@@ -3694,7 +3122,7 @@
       </c>
       <c r="L71" s="11"/>
     </row>
-    <row r="72" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="72" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B72" s="7"/>
       <c r="C72" s="5">
         <v>5206</v>
@@ -3711,7 +3139,7 @@
       <c r="G72" s="5">
         <v>203</v>
       </c>
-      <c r="H72" s="14" t="s">
+      <c r="H72" s="13" t="s">
         <v>36</v>
       </c>
       <c r="I72" s="10">
@@ -3725,7 +3153,7 @@
       </c>
       <c r="L72" s="11"/>
     </row>
-    <row r="73" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="73" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B73" s="7"/>
       <c r="C73" s="5">
         <v>5301</v>
@@ -3742,7 +3170,7 @@
       <c r="G73" s="5">
         <v>101</v>
       </c>
-      <c r="H73" s="14" t="s">
+      <c r="H73" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I73" s="10">
@@ -3756,7 +3184,7 @@
       </c>
       <c r="L73" s="11"/>
     </row>
-    <row r="74" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="74" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B74" s="7"/>
       <c r="C74" s="5">
         <v>5302</v>
@@ -3773,7 +3201,7 @@
       <c r="G74" s="5">
         <v>102</v>
       </c>
-      <c r="H74" s="14" t="s">
+      <c r="H74" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I74" s="10">
@@ -3787,7 +3215,7 @@
       </c>
       <c r="L74" s="11"/>
     </row>
-    <row r="75" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="75" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B75" s="7"/>
       <c r="C75" s="5">
         <v>5303</v>
@@ -3804,7 +3232,7 @@
       <c r="G75" s="5">
         <v>103</v>
       </c>
-      <c r="H75" s="14" t="s">
+      <c r="H75" s="13" t="s">
         <v>39</v>
       </c>
       <c r="I75" s="10">
@@ -3818,7 +3246,7 @@
       </c>
       <c r="L75" s="11"/>
     </row>
-    <row r="76" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="76" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B76" s="7"/>
       <c r="C76" s="5">
         <v>5304</v>
@@ -3835,7 +3263,7 @@
       <c r="G76" s="5">
         <v>201</v>
       </c>
-      <c r="H76" s="14" t="s">
+      <c r="H76" s="13" t="s">
         <v>40</v>
       </c>
       <c r="I76" s="10">
@@ -3849,7 +3277,7 @@
       </c>
       <c r="L76" s="11"/>
     </row>
-    <row r="77" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="77" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B77" s="7"/>
       <c r="C77" s="5">
         <v>5305</v>
@@ -3866,7 +3294,7 @@
       <c r="G77" s="5">
         <v>202</v>
       </c>
-      <c r="H77" s="14" t="s">
+      <c r="H77" s="13" t="s">
         <v>40</v>
       </c>
       <c r="I77" s="10">
@@ -3880,7 +3308,7 @@
       </c>
       <c r="L77" s="11"/>
     </row>
-    <row r="78" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="78" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B78" s="7"/>
       <c r="C78" s="5">
         <v>5306</v>
@@ -3897,7 +3325,7 @@
       <c r="G78" s="5">
         <v>203</v>
       </c>
-      <c r="H78" s="14" t="s">
+      <c r="H78" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I78" s="10">
@@ -3911,7 +3339,7 @@
       </c>
       <c r="L78" s="11"/>
     </row>
-    <row r="79" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="79" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B79" s="7"/>
       <c r="C79" s="5">
         <v>5401</v>
@@ -3928,7 +3356,7 @@
       <c r="G79" s="5">
         <v>101</v>
       </c>
-      <c r="H79" s="14" t="s">
+      <c r="H79" s="13" t="s">
         <v>42</v>
       </c>
       <c r="I79" s="10">
@@ -3942,7 +3370,7 @@
       </c>
       <c r="L79" s="11"/>
     </row>
-    <row r="80" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="80" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B80" s="7"/>
       <c r="C80" s="5">
         <v>5402</v>
@@ -3959,7 +3387,7 @@
       <c r="G80" s="5">
         <v>102</v>
       </c>
-      <c r="H80" s="14" t="s">
+      <c r="H80" s="13" t="s">
         <v>42</v>
       </c>
       <c r="I80" s="10">
@@ -3973,7 +3401,7 @@
       </c>
       <c r="L80" s="11"/>
     </row>
-    <row r="81" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="81" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B81" s="7"/>
       <c r="C81" s="5">
         <v>5403</v>
@@ -3990,7 +3418,7 @@
       <c r="G81" s="5">
         <v>103</v>
       </c>
-      <c r="H81" s="14" t="s">
+      <c r="H81" s="13" t="s">
         <v>44</v>
       </c>
       <c r="I81" s="10">
@@ -4004,7 +3432,7 @@
       </c>
       <c r="L81" s="11"/>
     </row>
-    <row r="82" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="82" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B82" s="7"/>
       <c r="C82" s="5">
         <v>5404</v>
@@ -4021,7 +3449,7 @@
       <c r="G82" s="5">
         <v>201</v>
       </c>
-      <c r="H82" s="14" t="s">
+      <c r="H82" s="13" t="s">
         <v>45</v>
       </c>
       <c r="I82" s="10">
@@ -4035,7 +3463,7 @@
       </c>
       <c r="L82" s="11"/>
     </row>
-    <row r="83" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="83" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B83" s="7"/>
       <c r="C83" s="5">
         <v>5405</v>
@@ -4052,7 +3480,7 @@
       <c r="G83" s="5">
         <v>202</v>
       </c>
-      <c r="H83" s="14" t="s">
+      <c r="H83" s="13" t="s">
         <v>45</v>
       </c>
       <c r="I83" s="10">
@@ -4066,7 +3494,7 @@
       </c>
       <c r="L83" s="11"/>
     </row>
-    <row r="84" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="84" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B84" s="7"/>
       <c r="C84" s="5">
         <v>5406</v>
@@ -4083,7 +3511,7 @@
       <c r="G84" s="5">
         <v>203</v>
       </c>
-      <c r="H84" s="14" t="s">
+      <c r="H84" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I84" s="10">
@@ -4097,7 +3525,7 @@
       </c>
       <c r="L84" s="11"/>
     </row>
-    <row r="85" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="85" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B85" s="7"/>
       <c r="C85" s="5">
         <v>5001</v>
@@ -4114,7 +3542,7 @@
       <c r="G85" s="5">
         <v>203</v>
       </c>
-      <c r="H85" s="14" t="s">
+      <c r="H85" s="13" t="s">
         <v>36</v>
       </c>
       <c r="I85" s="10">
@@ -4124,11 +3552,11 @@
         <v>5</v>
       </c>
       <c r="K85" s="5"/>
-      <c r="L85" s="17" t="s">
+      <c r="L85" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="86" ht="20.1" customHeight="1" spans="2:12">
+    <row r="86" spans="2:12" ht="20.100000000000001" customHeight="1">
       <c r="C86" s="5">
         <v>6001</v>
       </c>
@@ -4144,7 +3572,7 @@
       <c r="G86" s="3">
         <v>203</v>
       </c>
-      <c r="H86" s="14" t="s">
+      <c r="H86" s="13" t="s">
         <v>36</v>
       </c>
       <c r="I86" s="10">
@@ -4154,7 +3582,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="87" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B87" s="7"/>
       <c r="C87" s="5">
         <v>7001</v>
@@ -4181,7 +3609,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="9"/>
     </row>
-    <row r="88" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="88" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B88" s="7"/>
       <c r="C88" s="5">
         <v>8001</v>
@@ -4208,7 +3636,7 @@
       <c r="K88" s="5"/>
       <c r="L88" s="9"/>
     </row>
-    <row r="89" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="89" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B89" s="7"/>
       <c r="C89" s="5">
         <v>9001</v>
@@ -4225,7 +3653,7 @@
       <c r="G89" s="5">
         <v>0</v>
       </c>
-      <c r="H89" s="14" t="s">
+      <c r="H89" s="13" t="s">
         <v>45</v>
       </c>
       <c r="I89" s="5" t="s">
@@ -4235,11 +3663,11 @@
         <v>9</v>
       </c>
       <c r="K89" s="5"/>
-      <c r="L89" s="15" t="s">
+      <c r="L89" s="14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="90" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B90" s="7"/>
       <c r="C90" s="5">
         <v>10001</v>
@@ -4256,7 +3684,7 @@
       <c r="G90" s="5">
         <v>0</v>
       </c>
-      <c r="H90" s="14" t="s">
+      <c r="H90" s="13" t="s">
         <v>45</v>
       </c>
       <c r="I90" s="5" t="s">
@@ -4266,11 +3694,11 @@
         <v>10</v>
       </c>
       <c r="K90" s="5"/>
-      <c r="L90" s="15" t="s">
+      <c r="L90" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="91" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+    <row r="91" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B91" s="7"/>
       <c r="C91" s="5">
         <v>11001</v>
@@ -4287,7 +3715,7 @@
       <c r="G91" s="5">
         <v>0</v>
       </c>
-      <c r="H91" s="14" t="s">
+      <c r="H91" s="13" t="s">
         <v>45</v>
       </c>
       <c r="I91" s="5" t="s">
@@ -4297,14 +3725,14 @@
         <v>11</v>
       </c>
       <c r="K91" s="5"/>
-      <c r="L91" s="15" t="s">
+      <c r="L91" s="14" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/RobotConfig.xlsx
+++ b/Excel/RobotConfig.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA528769-0984-48FB-AE9D-482DDF4493B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="809"/>
   </bookViews>
   <sheets>
     <sheet name="RobotConfig" sheetId="1" r:id="rId1"/>
@@ -33,20 +27,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -55,7 +48,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -63,14 +55,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="J3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -79,7 +70,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -96,14 +86,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="K3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -112,7 +101,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -120,14 +108,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -136,7 +123,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -149,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
   <si>
     <t>cs</t>
   </si>
@@ -301,6 +287,12 @@
     <t>1250,1250,1250,1250,1250</t>
   </si>
   <si>
+    <t>190.75,29.92,-64.15</t>
+  </si>
+  <si>
+    <t>58.35,28.77,-128.42</t>
+  </si>
+  <si>
     <t>1-30级战场机器人</t>
   </si>
   <si>
@@ -343,17 +335,20 @@
     <t>宝藏之地机器人</t>
   </si>
   <si>
-    <t>58.35,28.77,-128.42</t>
-  </si>
-  <si>
-    <t>190.75,29.92,-64.15</t>
+    <t>主城出生点机器人</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,7 +360,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -373,68 +374,184 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -453,8 +570,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -475,77 +778,363 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 6" xfId="50"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -803,13 +1392,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L91"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -826,7 +1415,7 @@
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -842,7 +1431,7 @@
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -858,7 +1447,7 @@
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
@@ -892,7 +1481,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
@@ -926,7 +1515,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
@@ -960,7 +1549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B6" s="7"/>
       <c r="C6" s="5">
         <v>1001</v>
@@ -987,7 +1576,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="9"/>
     </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B7" s="7"/>
       <c r="C7" s="5">
         <v>2101</v>
@@ -1004,7 +1593,7 @@
       <c r="G7" s="5">
         <v>101</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I7" s="10">
@@ -1016,11 +1605,11 @@
       <c r="K7" s="5">
         <v>110001</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B8" s="7"/>
       <c r="C8" s="5">
         <v>2102</v>
@@ -1037,7 +1626,7 @@
       <c r="G8" s="5">
         <v>102</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="10">
@@ -1049,11 +1638,11 @@
       <c r="K8" s="5">
         <v>110001</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B9" s="7"/>
       <c r="C9" s="5">
         <v>2103</v>
@@ -1070,7 +1659,7 @@
       <c r="G9" s="5">
         <v>103</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="14" t="s">
         <v>29</v>
       </c>
       <c r="I9" s="10">
@@ -1082,11 +1671,11 @@
       <c r="K9" s="5">
         <v>110001</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B10" s="7"/>
       <c r="C10" s="5">
         <v>2104</v>
@@ -1103,7 +1692,7 @@
       <c r="G10" s="5">
         <v>201</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="10">
@@ -1115,11 +1704,11 @@
       <c r="K10" s="5">
         <v>110001</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B11" s="7"/>
       <c r="C11" s="5">
         <v>2105</v>
@@ -1136,7 +1725,7 @@
       <c r="G11" s="5">
         <v>202</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="10">
@@ -1148,11 +1737,11 @@
       <c r="K11" s="5">
         <v>110001</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B12" s="7"/>
       <c r="C12" s="5">
         <v>2106</v>
@@ -1169,7 +1758,7 @@
       <c r="G12" s="5">
         <v>203</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="10">
@@ -1181,11 +1770,11 @@
       <c r="K12" s="5">
         <v>110001</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B13" s="7"/>
       <c r="C13" s="5">
         <f>C7+100</f>
@@ -1203,7 +1792,7 @@
       <c r="G13" s="5">
         <v>101</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="10">
@@ -1215,11 +1804,11 @@
       <c r="K13" s="5">
         <v>110002</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B14" s="7"/>
       <c r="C14" s="5">
         <f t="shared" ref="C14:C48" si="0">C8+100</f>
@@ -1237,7 +1826,7 @@
       <c r="G14" s="5">
         <v>102</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="10">
@@ -1249,11 +1838,11 @@
       <c r="K14" s="5">
         <v>110002</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B15" s="7"/>
       <c r="C15" s="5">
         <f t="shared" si="0"/>
@@ -1271,7 +1860,7 @@
       <c r="G15" s="5">
         <v>103</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="14" t="s">
         <v>34</v>
       </c>
       <c r="I15" s="10">
@@ -1283,11 +1872,11 @@
       <c r="K15" s="5">
         <v>110002</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:12">
       <c r="B16" s="7"/>
       <c r="C16" s="5">
         <f t="shared" si="0"/>
@@ -1305,7 +1894,7 @@
       <c r="G16" s="5">
         <v>201</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="10">
@@ -1317,11 +1906,11 @@
       <c r="K16" s="5">
         <v>110002</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B17" s="7"/>
       <c r="C17" s="5">
         <f t="shared" si="0"/>
@@ -1339,7 +1928,7 @@
       <c r="G17" s="5">
         <v>202</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H17" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="10">
@@ -1351,11 +1940,11 @@
       <c r="K17" s="5">
         <v>110002</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B18" s="7"/>
       <c r="C18" s="5">
         <f t="shared" si="0"/>
@@ -1373,7 +1962,7 @@
       <c r="G18" s="5">
         <v>203</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="H18" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I18" s="10">
@@ -1385,11 +1974,11 @@
       <c r="K18" s="5">
         <v>110002</v>
       </c>
-      <c r="L18" s="14" t="s">
+      <c r="L18" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="19" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B19" s="7"/>
       <c r="C19" s="5">
         <f t="shared" si="0"/>
@@ -1407,7 +1996,7 @@
       <c r="G19" s="5">
         <v>101</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H19" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I19" s="10">
@@ -1419,11 +2008,11 @@
       <c r="K19" s="5">
         <v>110003</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L19" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B20" s="7"/>
       <c r="C20" s="5">
         <f t="shared" si="0"/>
@@ -1441,7 +2030,7 @@
       <c r="G20" s="5">
         <v>102</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="10">
@@ -1453,11 +2042,11 @@
       <c r="K20" s="5">
         <v>110003</v>
       </c>
-      <c r="L20" s="14" t="s">
+      <c r="L20" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="21" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B21" s="7"/>
       <c r="C21" s="5">
         <f t="shared" si="0"/>
@@ -1475,7 +2064,7 @@
       <c r="G21" s="5">
         <v>103</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="14" t="s">
         <v>39</v>
       </c>
       <c r="I21" s="10">
@@ -1487,11 +2076,11 @@
       <c r="K21" s="5">
         <v>110003</v>
       </c>
-      <c r="L21" s="14" t="s">
+      <c r="L21" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="22" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B22" s="7"/>
       <c r="C22" s="5">
         <f t="shared" si="0"/>
@@ -1509,7 +2098,7 @@
       <c r="G22" s="5">
         <v>201</v>
       </c>
-      <c r="H22" s="13" t="s">
+      <c r="H22" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I22" s="10">
@@ -1521,11 +2110,11 @@
       <c r="K22" s="5">
         <v>110003</v>
       </c>
-      <c r="L22" s="14" t="s">
+      <c r="L22" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="23" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B23" s="7"/>
       <c r="C23" s="5">
         <f t="shared" si="0"/>
@@ -1543,7 +2132,7 @@
       <c r="G23" s="5">
         <v>202</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I23" s="10">
@@ -1555,11 +2144,11 @@
       <c r="K23" s="5">
         <v>110003</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="24" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B24" s="7"/>
       <c r="C24" s="5">
         <f t="shared" si="0"/>
@@ -1577,7 +2166,7 @@
       <c r="G24" s="5">
         <v>203</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="14" t="s">
         <v>41</v>
       </c>
       <c r="I24" s="10">
@@ -1589,11 +2178,11 @@
       <c r="K24" s="5">
         <v>110003</v>
       </c>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="15" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="25" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B25" s="7"/>
       <c r="C25" s="5">
         <f t="shared" si="0"/>
@@ -1611,7 +2200,7 @@
       <c r="G25" s="5">
         <v>101</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="14" t="s">
         <v>42</v>
       </c>
       <c r="I25" s="10">
@@ -1623,11 +2212,11 @@
       <c r="K25" s="5">
         <v>110004</v>
       </c>
-      <c r="L25" s="14" t="s">
+      <c r="L25" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="26" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B26" s="7"/>
       <c r="C26" s="5">
         <f t="shared" si="0"/>
@@ -1645,7 +2234,7 @@
       <c r="G26" s="5">
         <v>102</v>
       </c>
-      <c r="H26" s="13" t="s">
+      <c r="H26" s="14" t="s">
         <v>42</v>
       </c>
       <c r="I26" s="10">
@@ -1657,11 +2246,11 @@
       <c r="K26" s="5">
         <v>110004</v>
       </c>
-      <c r="L26" s="14" t="s">
+      <c r="L26" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B27" s="7"/>
       <c r="C27" s="5">
         <f t="shared" si="0"/>
@@ -1679,7 +2268,7 @@
       <c r="G27" s="5">
         <v>103</v>
       </c>
-      <c r="H27" s="13" t="s">
+      <c r="H27" s="14" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="10">
@@ -1691,11 +2280,11 @@
       <c r="K27" s="5">
         <v>110004</v>
       </c>
-      <c r="L27" s="14" t="s">
+      <c r="L27" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="28" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B28" s="7"/>
       <c r="C28" s="5">
         <f t="shared" si="0"/>
@@ -1713,7 +2302,7 @@
       <c r="G28" s="5">
         <v>201</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I28" s="10">
@@ -1725,11 +2314,11 @@
       <c r="K28" s="5">
         <v>110004</v>
       </c>
-      <c r="L28" s="14" t="s">
+      <c r="L28" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="29" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B29" s="7"/>
       <c r="C29" s="5">
         <f t="shared" si="0"/>
@@ -1747,7 +2336,7 @@
       <c r="G29" s="5">
         <v>202</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H29" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I29" s="10">
@@ -1759,11 +2348,11 @@
       <c r="K29" s="5">
         <v>110004</v>
       </c>
-      <c r="L29" s="14" t="s">
+      <c r="L29" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="30" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B30" s="7"/>
       <c r="C30" s="5">
         <f t="shared" si="0"/>
@@ -1781,7 +2370,7 @@
       <c r="G30" s="5">
         <v>203</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="14" t="s">
         <v>46</v>
       </c>
       <c r="I30" s="10">
@@ -1793,11 +2382,11 @@
       <c r="K30" s="5">
         <v>110004</v>
       </c>
-      <c r="L30" s="14" t="s">
+      <c r="L30" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="31" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B31" s="7"/>
       <c r="C31" s="5">
         <f t="shared" si="0"/>
@@ -1815,10 +2404,10 @@
       <c r="G31" s="5">
         <v>101</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J31" s="8">
@@ -1827,11 +2416,11 @@
       <c r="K31" s="5">
         <v>110005</v>
       </c>
-      <c r="L31" s="14" t="s">
+      <c r="L31" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="32" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B32" s="7"/>
       <c r="C32" s="5">
         <f t="shared" si="0"/>
@@ -1849,10 +2438,10 @@
       <c r="G32" s="5">
         <v>102</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="H32" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J32" s="8">
@@ -1861,11 +2450,11 @@
       <c r="K32" s="5">
         <v>110005</v>
       </c>
-      <c r="L32" s="14" t="s">
+      <c r="L32" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="33" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B33" s="7"/>
       <c r="C33" s="5">
         <f t="shared" si="0"/>
@@ -1883,10 +2472,10 @@
       <c r="G33" s="5">
         <v>103</v>
       </c>
-      <c r="H33" s="13" t="s">
+      <c r="H33" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J33" s="8">
@@ -1895,11 +2484,11 @@
       <c r="K33" s="5">
         <v>110005</v>
       </c>
-      <c r="L33" s="14" t="s">
+      <c r="L33" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="34" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B34" s="7"/>
       <c r="C34" s="5">
         <f t="shared" si="0"/>
@@ -1917,10 +2506,10 @@
       <c r="G34" s="5">
         <v>201</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="I34" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J34" s="8">
@@ -1929,11 +2518,11 @@
       <c r="K34" s="5">
         <v>110005</v>
       </c>
-      <c r="L34" s="14" t="s">
+      <c r="L34" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="35" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B35" s="7"/>
       <c r="C35" s="5">
         <f t="shared" si="0"/>
@@ -1951,10 +2540,10 @@
       <c r="G35" s="5">
         <v>202</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H35" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J35" s="8">
@@ -1963,11 +2552,11 @@
       <c r="K35" s="5">
         <v>110005</v>
       </c>
-      <c r="L35" s="14" t="s">
+      <c r="L35" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="36" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B36" s="7"/>
       <c r="C36" s="5">
         <f t="shared" si="0"/>
@@ -1985,10 +2574,10 @@
       <c r="G36" s="5">
         <v>203</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="H36" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="16" t="s">
         <v>47</v>
       </c>
       <c r="J36" s="8">
@@ -1997,11 +2586,11 @@
       <c r="K36" s="5">
         <v>110005</v>
       </c>
-      <c r="L36" s="14" t="s">
+      <c r="L36" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="37" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B37" s="7"/>
       <c r="C37" s="5">
         <f t="shared" si="0"/>
@@ -2019,10 +2608,10 @@
       <c r="G37" s="5">
         <v>101</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="I37" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J37" s="8">
@@ -2031,11 +2620,11 @@
       <c r="K37" s="5">
         <v>110006</v>
       </c>
-      <c r="L37" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L37" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B38" s="7"/>
       <c r="C38" s="5">
         <f t="shared" si="0"/>
@@ -2053,10 +2642,10 @@
       <c r="G38" s="5">
         <v>102</v>
       </c>
-      <c r="H38" s="13" t="s">
+      <c r="H38" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="I38" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J38" s="8">
@@ -2065,11 +2654,11 @@
       <c r="K38" s="5">
         <v>110006</v>
       </c>
-      <c r="L38" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L38" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B39" s="7"/>
       <c r="C39" s="5">
         <f t="shared" si="0"/>
@@ -2087,10 +2676,10 @@
       <c r="G39" s="5">
         <v>103</v>
       </c>
-      <c r="H39" s="13" t="s">
+      <c r="H39" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J39" s="8">
@@ -2099,11 +2688,11 @@
       <c r="K39" s="5">
         <v>110006</v>
       </c>
-      <c r="L39" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L39" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B40" s="7"/>
       <c r="C40" s="5">
         <f t="shared" si="0"/>
@@ -2121,10 +2710,10 @@
       <c r="G40" s="5">
         <v>201</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J40" s="8">
@@ -2133,11 +2722,11 @@
       <c r="K40" s="5">
         <v>110006</v>
       </c>
-      <c r="L40" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L40" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B41" s="7"/>
       <c r="C41" s="5">
         <f t="shared" si="0"/>
@@ -2155,10 +2744,10 @@
       <c r="G41" s="5">
         <v>202</v>
       </c>
-      <c r="H41" s="13" t="s">
+      <c r="H41" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="I41" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="8">
@@ -2167,11 +2756,11 @@
       <c r="K41" s="5">
         <v>110006</v>
       </c>
-      <c r="L41" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L41" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B42" s="7"/>
       <c r="C42" s="5">
         <f t="shared" si="0"/>
@@ -2189,10 +2778,10 @@
       <c r="G42" s="5">
         <v>203</v>
       </c>
-      <c r="H42" s="13" t="s">
+      <c r="H42" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="I42" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J42" s="8">
@@ -2201,11 +2790,11 @@
       <c r="K42" s="5">
         <v>110006</v>
       </c>
-      <c r="L42" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L42" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B43" s="7"/>
       <c r="C43" s="5">
         <f t="shared" si="0"/>
@@ -2223,23 +2812,23 @@
       <c r="G43" s="5">
         <v>101</v>
       </c>
-      <c r="H43" s="13" t="s">
+      <c r="H43" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="I43" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J43" s="8">
         <v>2</v>
       </c>
-      <c r="K43" s="12">
+      <c r="K43" s="5">
         <v>110007</v>
       </c>
-      <c r="L43" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L43" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B44" s="7"/>
       <c r="C44" s="5">
         <f t="shared" si="0"/>
@@ -2257,23 +2846,23 @@
       <c r="G44" s="5">
         <v>102</v>
       </c>
-      <c r="H44" s="13" t="s">
+      <c r="H44" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I44" s="15" t="s">
+      <c r="I44" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J44" s="8">
         <v>2</v>
       </c>
-      <c r="K44" s="12">
+      <c r="K44" s="5">
         <v>110007</v>
       </c>
-      <c r="L44" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L44" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B45" s="7"/>
       <c r="C45" s="5">
         <f t="shared" si="0"/>
@@ -2291,23 +2880,23 @@
       <c r="G45" s="5">
         <v>103</v>
       </c>
-      <c r="H45" s="13" t="s">
+      <c r="H45" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I45" s="15" t="s">
+      <c r="I45" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J45" s="8">
         <v>2</v>
       </c>
-      <c r="K45" s="12">
+      <c r="K45" s="5">
         <v>110007</v>
       </c>
-      <c r="L45" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L45" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B46" s="7"/>
       <c r="C46" s="5">
         <f t="shared" si="0"/>
@@ -2325,23 +2914,23 @@
       <c r="G46" s="5">
         <v>201</v>
       </c>
-      <c r="H46" s="13" t="s">
+      <c r="H46" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I46" s="15" t="s">
+      <c r="I46" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J46" s="8">
         <v>2</v>
       </c>
-      <c r="K46" s="12">
+      <c r="K46" s="5">
         <v>110007</v>
       </c>
-      <c r="L46" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L46" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B47" s="7"/>
       <c r="C47" s="5">
         <f t="shared" si="0"/>
@@ -2359,23 +2948,23 @@
       <c r="G47" s="5">
         <v>202</v>
       </c>
-      <c r="H47" s="13" t="s">
+      <c r="H47" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I47" s="15" t="s">
+      <c r="I47" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J47" s="8">
         <v>2</v>
       </c>
-      <c r="K47" s="12">
+      <c r="K47" s="5">
         <v>110007</v>
       </c>
-      <c r="L47" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L47" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B48" s="7"/>
       <c r="C48" s="5">
         <f t="shared" si="0"/>
@@ -2393,23 +2982,23 @@
       <c r="G48" s="5">
         <v>203</v>
       </c>
-      <c r="H48" s="13" t="s">
+      <c r="H48" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I48" s="15" t="s">
+      <c r="I48" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J48" s="8">
         <v>2</v>
       </c>
-      <c r="K48" s="12">
+      <c r="K48" s="5">
         <v>110007</v>
       </c>
-      <c r="L48" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L48" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B49" s="7"/>
       <c r="C49" s="5">
         <v>3001</v>
@@ -2418,7 +3007,7 @@
         <v>20</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F49" s="5">
         <v>1</v>
@@ -2426,7 +3015,7 @@
       <c r="G49" s="5">
         <v>101</v>
       </c>
-      <c r="H49" s="13" t="s">
+      <c r="H49" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I49" s="10">
@@ -2436,11 +3025,11 @@
         <v>3</v>
       </c>
       <c r="K49" s="5"/>
-      <c r="L49" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="50" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L49" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B50" s="7"/>
       <c r="C50" s="5">
         <v>3002</v>
@@ -2449,7 +3038,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F50" s="5">
         <v>1</v>
@@ -2457,7 +3046,7 @@
       <c r="G50" s="5">
         <v>102</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="H50" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I50" s="10">
@@ -2467,11 +3056,11 @@
         <v>3</v>
       </c>
       <c r="K50" s="5"/>
-      <c r="L50" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L50" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B51" s="7"/>
       <c r="C51" s="5">
         <v>3003</v>
@@ -2480,7 +3069,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F51" s="5">
         <v>1</v>
@@ -2488,7 +3077,7 @@
       <c r="G51" s="5">
         <v>103</v>
       </c>
-      <c r="H51" s="13" t="s">
+      <c r="H51" s="14" t="s">
         <v>29</v>
       </c>
       <c r="I51" s="10">
@@ -2498,11 +3087,11 @@
         <v>3</v>
       </c>
       <c r="K51" s="5"/>
-      <c r="L51" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L51" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B52" s="7"/>
       <c r="C52" s="5">
         <v>3004</v>
@@ -2511,7 +3100,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F52" s="5">
         <v>2</v>
@@ -2519,7 +3108,7 @@
       <c r="G52" s="5">
         <v>201</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="H52" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I52" s="10">
@@ -2529,11 +3118,11 @@
         <v>3</v>
       </c>
       <c r="K52" s="5"/>
-      <c r="L52" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L52" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B53" s="7"/>
       <c r="C53" s="5">
         <v>3005</v>
@@ -2542,7 +3131,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F53" s="5">
         <v>2</v>
@@ -2550,7 +3139,7 @@
       <c r="G53" s="5">
         <v>202</v>
       </c>
-      <c r="H53" s="13" t="s">
+      <c r="H53" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="10">
@@ -2560,11 +3149,11 @@
         <v>3</v>
       </c>
       <c r="K53" s="5"/>
-      <c r="L53" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L53" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B54" s="7"/>
       <c r="C54" s="5">
         <v>3006</v>
@@ -2573,7 +3162,7 @@
         <v>20</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F54" s="5">
         <v>2</v>
@@ -2581,7 +3170,7 @@
       <c r="G54" s="5">
         <v>203</v>
       </c>
-      <c r="H54" s="13" t="s">
+      <c r="H54" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="10">
@@ -2591,11 +3180,11 @@
         <v>3</v>
       </c>
       <c r="K54" s="5"/>
-      <c r="L54" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L54" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B55" s="7"/>
       <c r="C55" s="5">
         <v>3051</v>
@@ -2604,7 +3193,7 @@
         <v>30</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F55" s="5">
         <v>1</v>
@@ -2612,7 +3201,7 @@
       <c r="G55" s="5">
         <v>101</v>
       </c>
-      <c r="H55" s="13" t="s">
+      <c r="H55" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I55" s="10">
@@ -2622,11 +3211,11 @@
         <v>3</v>
       </c>
       <c r="K55" s="5"/>
-      <c r="L55" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L55" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B56" s="7"/>
       <c r="C56" s="5">
         <v>3052</v>
@@ -2635,7 +3224,7 @@
         <v>30</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F56" s="5">
         <v>1</v>
@@ -2643,7 +3232,7 @@
       <c r="G56" s="5">
         <v>102</v>
       </c>
-      <c r="H56" s="13" t="s">
+      <c r="H56" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I56" s="10">
@@ -2653,11 +3242,11 @@
         <v>3</v>
       </c>
       <c r="K56" s="5"/>
-      <c r="L56" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L56" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B57" s="7"/>
       <c r="C57" s="5">
         <v>3053</v>
@@ -2666,7 +3255,7 @@
         <v>30</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F57" s="5">
         <v>1</v>
@@ -2674,7 +3263,7 @@
       <c r="G57" s="5">
         <v>103</v>
       </c>
-      <c r="H57" s="13" t="s">
+      <c r="H57" s="14" t="s">
         <v>34</v>
       </c>
       <c r="I57" s="10">
@@ -2684,11 +3273,11 @@
         <v>3</v>
       </c>
       <c r="K57" s="5"/>
-      <c r="L57" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L57" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B58" s="7"/>
       <c r="C58" s="5">
         <v>3054</v>
@@ -2697,7 +3286,7 @@
         <v>30</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F58" s="5">
         <v>2</v>
@@ -2705,7 +3294,7 @@
       <c r="G58" s="5">
         <v>201</v>
       </c>
-      <c r="H58" s="13" t="s">
+      <c r="H58" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I58" s="10">
@@ -2715,11 +3304,11 @@
         <v>3</v>
       </c>
       <c r="K58" s="5"/>
-      <c r="L58" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L58" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B59" s="7"/>
       <c r="C59" s="5">
         <v>3055</v>
@@ -2728,7 +3317,7 @@
         <v>30</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F59" s="5">
         <v>2</v>
@@ -2736,7 +3325,7 @@
       <c r="G59" s="5">
         <v>202</v>
       </c>
-      <c r="H59" s="13" t="s">
+      <c r="H59" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I59" s="10">
@@ -2746,11 +3335,11 @@
         <v>3</v>
       </c>
       <c r="K59" s="5"/>
-      <c r="L59" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="60" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L59" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B60" s="7"/>
       <c r="C60" s="5">
         <v>3056</v>
@@ -2759,7 +3348,7 @@
         <v>30</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F60" s="5">
         <v>2</v>
@@ -2767,7 +3356,7 @@
       <c r="G60" s="5">
         <v>203</v>
       </c>
-      <c r="H60" s="13" t="s">
+      <c r="H60" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I60" s="10">
@@ -2777,11 +3366,11 @@
         <v>3</v>
       </c>
       <c r="K60" s="5"/>
-      <c r="L60" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L60" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B61" s="7"/>
       <c r="C61" s="5">
         <v>5101</v>
@@ -2790,7 +3379,7 @@
         <v>20</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F61" s="5">
         <v>1</v>
@@ -2798,11 +3387,11 @@
       <c r="G61" s="5">
         <v>101</v>
       </c>
-      <c r="H61" s="13" t="s">
+      <c r="H61" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J61" s="5">
         <v>4</v>
@@ -2812,7 +3401,7 @@
       </c>
       <c r="L61" s="11"/>
     </row>
-    <row r="62" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="62" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B62" s="7"/>
       <c r="C62" s="5">
         <v>5102</v>
@@ -2821,7 +3410,7 @@
         <v>20</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F62" s="5">
         <v>1</v>
@@ -2829,11 +3418,11 @@
       <c r="G62" s="5">
         <v>102</v>
       </c>
-      <c r="H62" s="13" t="s">
+      <c r="H62" s="14" t="s">
         <v>27</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J62" s="5">
         <v>4</v>
@@ -2843,7 +3432,7 @@
       </c>
       <c r="L62" s="11"/>
     </row>
-    <row r="63" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="63" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B63" s="7"/>
       <c r="C63" s="5">
         <v>5103</v>
@@ -2852,7 +3441,7 @@
         <v>20</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F63" s="5">
         <v>1</v>
@@ -2860,11 +3449,11 @@
       <c r="G63" s="5">
         <v>103</v>
       </c>
-      <c r="H63" s="13" t="s">
+      <c r="H63" s="14" t="s">
         <v>29</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J63" s="5">
         <v>4</v>
@@ -2874,7 +3463,7 @@
       </c>
       <c r="L63" s="11"/>
     </row>
-    <row r="64" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="64" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B64" s="7"/>
       <c r="C64" s="5">
         <v>5104</v>
@@ -2883,7 +3472,7 @@
         <v>20</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F64" s="5">
         <v>2</v>
@@ -2891,11 +3480,11 @@
       <c r="G64" s="5">
         <v>201</v>
       </c>
-      <c r="H64" s="13" t="s">
+      <c r="H64" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J64" s="5">
         <v>4</v>
@@ -2905,7 +3494,7 @@
       </c>
       <c r="L64" s="11"/>
     </row>
-    <row r="65" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="65" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B65" s="7"/>
       <c r="C65" s="5">
         <v>5105</v>
@@ -2914,7 +3503,7 @@
         <v>20</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F65" s="5">
         <v>2</v>
@@ -2922,11 +3511,11 @@
       <c r="G65" s="5">
         <v>202</v>
       </c>
-      <c r="H65" s="13" t="s">
+      <c r="H65" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J65" s="5">
         <v>4</v>
@@ -2936,7 +3525,7 @@
       </c>
       <c r="L65" s="11"/>
     </row>
-    <row r="66" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="66" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B66" s="7"/>
       <c r="C66" s="5">
         <v>5106</v>
@@ -2945,7 +3534,7 @@
         <v>20</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F66" s="5">
         <v>2</v>
@@ -2953,11 +3542,11 @@
       <c r="G66" s="5">
         <v>203</v>
       </c>
-      <c r="H66" s="13" t="s">
+      <c r="H66" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J66" s="5">
         <v>4</v>
@@ -2967,7 +3556,7 @@
       </c>
       <c r="L66" s="11"/>
     </row>
-    <row r="67" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="67" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B67" s="7"/>
       <c r="C67" s="5">
         <v>5201</v>
@@ -2976,7 +3565,7 @@
         <v>35</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F67" s="5">
         <v>1</v>
@@ -2984,7 +3573,7 @@
       <c r="G67" s="5">
         <v>101</v>
       </c>
-      <c r="H67" s="13" t="s">
+      <c r="H67" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I67" s="10">
@@ -2998,7 +3587,7 @@
       </c>
       <c r="L67" s="11"/>
     </row>
-    <row r="68" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="68" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B68" s="7"/>
       <c r="C68" s="5">
         <v>5202</v>
@@ -3007,7 +3596,7 @@
         <v>35</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F68" s="5">
         <v>1</v>
@@ -3015,7 +3604,7 @@
       <c r="G68" s="5">
         <v>102</v>
       </c>
-      <c r="H68" s="13" t="s">
+      <c r="H68" s="14" t="s">
         <v>32</v>
       </c>
       <c r="I68" s="10">
@@ -3029,7 +3618,7 @@
       </c>
       <c r="L68" s="11"/>
     </row>
-    <row r="69" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="69" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B69" s="7"/>
       <c r="C69" s="5">
         <v>5203</v>
@@ -3038,7 +3627,7 @@
         <v>35</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F69" s="5">
         <v>1</v>
@@ -3046,7 +3635,7 @@
       <c r="G69" s="5">
         <v>103</v>
       </c>
-      <c r="H69" s="13" t="s">
+      <c r="H69" s="14" t="s">
         <v>34</v>
       </c>
       <c r="I69" s="10">
@@ -3060,7 +3649,7 @@
       </c>
       <c r="L69" s="11"/>
     </row>
-    <row r="70" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="70" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B70" s="7"/>
       <c r="C70" s="5">
         <v>5204</v>
@@ -3069,7 +3658,7 @@
         <v>35</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F70" s="5">
         <v>2</v>
@@ -3077,7 +3666,7 @@
       <c r="G70" s="5">
         <v>201</v>
       </c>
-      <c r="H70" s="13" t="s">
+      <c r="H70" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I70" s="10">
@@ -3091,7 +3680,7 @@
       </c>
       <c r="L70" s="11"/>
     </row>
-    <row r="71" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="71" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B71" s="7"/>
       <c r="C71" s="5">
         <v>5205</v>
@@ -3100,7 +3689,7 @@
         <v>35</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F71" s="5">
         <v>2</v>
@@ -3108,7 +3697,7 @@
       <c r="G71" s="5">
         <v>202</v>
       </c>
-      <c r="H71" s="13" t="s">
+      <c r="H71" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I71" s="10">
@@ -3122,7 +3711,7 @@
       </c>
       <c r="L71" s="11"/>
     </row>
-    <row r="72" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="72" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B72" s="7"/>
       <c r="C72" s="5">
         <v>5206</v>
@@ -3131,7 +3720,7 @@
         <v>35</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F72" s="5">
         <v>2</v>
@@ -3139,7 +3728,7 @@
       <c r="G72" s="5">
         <v>203</v>
       </c>
-      <c r="H72" s="13" t="s">
+      <c r="H72" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I72" s="10">
@@ -3153,7 +3742,7 @@
       </c>
       <c r="L72" s="11"/>
     </row>
-    <row r="73" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="73" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B73" s="7"/>
       <c r="C73" s="5">
         <v>5301</v>
@@ -3162,7 +3751,7 @@
         <v>45</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F73" s="5">
         <v>1</v>
@@ -3170,7 +3759,7 @@
       <c r="G73" s="5">
         <v>101</v>
       </c>
-      <c r="H73" s="13" t="s">
+      <c r="H73" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I73" s="10">
@@ -3184,7 +3773,7 @@
       </c>
       <c r="L73" s="11"/>
     </row>
-    <row r="74" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="74" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B74" s="7"/>
       <c r="C74" s="5">
         <v>5302</v>
@@ -3193,7 +3782,7 @@
         <v>45</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F74" s="5">
         <v>1</v>
@@ -3201,7 +3790,7 @@
       <c r="G74" s="5">
         <v>102</v>
       </c>
-      <c r="H74" s="13" t="s">
+      <c r="H74" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I74" s="10">
@@ -3215,7 +3804,7 @@
       </c>
       <c r="L74" s="11"/>
     </row>
-    <row r="75" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="75" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B75" s="7"/>
       <c r="C75" s="5">
         <v>5303</v>
@@ -3224,7 +3813,7 @@
         <v>45</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F75" s="5">
         <v>1</v>
@@ -3232,7 +3821,7 @@
       <c r="G75" s="5">
         <v>103</v>
       </c>
-      <c r="H75" s="13" t="s">
+      <c r="H75" s="14" t="s">
         <v>39</v>
       </c>
       <c r="I75" s="10">
@@ -3246,7 +3835,7 @@
       </c>
       <c r="L75" s="11"/>
     </row>
-    <row r="76" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="76" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B76" s="7"/>
       <c r="C76" s="5">
         <v>5304</v>
@@ -3255,7 +3844,7 @@
         <v>45</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F76" s="5">
         <v>2</v>
@@ -3263,7 +3852,7 @@
       <c r="G76" s="5">
         <v>201</v>
       </c>
-      <c r="H76" s="13" t="s">
+      <c r="H76" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I76" s="10">
@@ -3277,7 +3866,7 @@
       </c>
       <c r="L76" s="11"/>
     </row>
-    <row r="77" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="77" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B77" s="7"/>
       <c r="C77" s="5">
         <v>5305</v>
@@ -3286,7 +3875,7 @@
         <v>45</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F77" s="5">
         <v>2</v>
@@ -3294,7 +3883,7 @@
       <c r="G77" s="5">
         <v>202</v>
       </c>
-      <c r="H77" s="13" t="s">
+      <c r="H77" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I77" s="10">
@@ -3308,7 +3897,7 @@
       </c>
       <c r="L77" s="11"/>
     </row>
-    <row r="78" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="78" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B78" s="7"/>
       <c r="C78" s="5">
         <v>5306</v>
@@ -3317,7 +3906,7 @@
         <v>45</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F78" s="5">
         <v>2</v>
@@ -3325,7 +3914,7 @@
       <c r="G78" s="5">
         <v>203</v>
       </c>
-      <c r="H78" s="13" t="s">
+      <c r="H78" s="14" t="s">
         <v>41</v>
       </c>
       <c r="I78" s="10">
@@ -3339,7 +3928,7 @@
       </c>
       <c r="L78" s="11"/>
     </row>
-    <row r="79" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="79" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B79" s="7"/>
       <c r="C79" s="5">
         <v>5401</v>
@@ -3348,7 +3937,7 @@
         <v>55</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F79" s="5">
         <v>1</v>
@@ -3356,7 +3945,7 @@
       <c r="G79" s="5">
         <v>101</v>
       </c>
-      <c r="H79" s="13" t="s">
+      <c r="H79" s="14" t="s">
         <v>42</v>
       </c>
       <c r="I79" s="10">
@@ -3370,7 +3959,7 @@
       </c>
       <c r="L79" s="11"/>
     </row>
-    <row r="80" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="80" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B80" s="7"/>
       <c r="C80" s="5">
         <v>5402</v>
@@ -3379,7 +3968,7 @@
         <v>55</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F80" s="5">
         <v>1</v>
@@ -3387,7 +3976,7 @@
       <c r="G80" s="5">
         <v>102</v>
       </c>
-      <c r="H80" s="13" t="s">
+      <c r="H80" s="14" t="s">
         <v>42</v>
       </c>
       <c r="I80" s="10">
@@ -3401,7 +3990,7 @@
       </c>
       <c r="L80" s="11"/>
     </row>
-    <row r="81" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="81" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B81" s="7"/>
       <c r="C81" s="5">
         <v>5403</v>
@@ -3410,7 +3999,7 @@
         <v>55</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F81" s="5">
         <v>1</v>
@@ -3418,7 +4007,7 @@
       <c r="G81" s="5">
         <v>103</v>
       </c>
-      <c r="H81" s="13" t="s">
+      <c r="H81" s="14" t="s">
         <v>44</v>
       </c>
       <c r="I81" s="10">
@@ -3432,7 +4021,7 @@
       </c>
       <c r="L81" s="11"/>
     </row>
-    <row r="82" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="82" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B82" s="7"/>
       <c r="C82" s="5">
         <v>5404</v>
@@ -3441,7 +4030,7 @@
         <v>55</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F82" s="5">
         <v>2</v>
@@ -3449,7 +4038,7 @@
       <c r="G82" s="5">
         <v>201</v>
       </c>
-      <c r="H82" s="13" t="s">
+      <c r="H82" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I82" s="10">
@@ -3463,7 +4052,7 @@
       </c>
       <c r="L82" s="11"/>
     </row>
-    <row r="83" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="83" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B83" s="7"/>
       <c r="C83" s="5">
         <v>5405</v>
@@ -3472,7 +4061,7 @@
         <v>55</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F83" s="5">
         <v>2</v>
@@ -3480,7 +4069,7 @@
       <c r="G83" s="5">
         <v>202</v>
       </c>
-      <c r="H83" s="13" t="s">
+      <c r="H83" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I83" s="10">
@@ -3494,7 +4083,7 @@
       </c>
       <c r="L83" s="11"/>
     </row>
-    <row r="84" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="84" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B84" s="7"/>
       <c r="C84" s="5">
         <v>5406</v>
@@ -3503,7 +4092,7 @@
         <v>55</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F84" s="5">
         <v>2</v>
@@ -3511,7 +4100,7 @@
       <c r="G84" s="5">
         <v>203</v>
       </c>
-      <c r="H84" s="13" t="s">
+      <c r="H84" s="14" t="s">
         <v>46</v>
       </c>
       <c r="I84" s="10">
@@ -3525,7 +4114,7 @@
       </c>
       <c r="L84" s="11"/>
     </row>
-    <row r="85" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="85" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B85" s="7"/>
       <c r="C85" s="5">
         <v>5001</v>
@@ -3534,7 +4123,7 @@
         <v>30</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F85" s="5">
         <v>2</v>
@@ -3542,7 +4131,7 @@
       <c r="G85" s="5">
         <v>203</v>
       </c>
-      <c r="H85" s="13" t="s">
+      <c r="H85" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I85" s="10">
@@ -3552,11 +4141,11 @@
         <v>5</v>
       </c>
       <c r="K85" s="5"/>
-      <c r="L85" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="86" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="L85" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" ht="20.1" customHeight="1" spans="2:12">
       <c r="C86" s="5">
         <v>6001</v>
       </c>
@@ -3564,7 +4153,7 @@
         <v>40</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F86" s="3">
         <v>2</v>
@@ -3572,7 +4161,7 @@
       <c r="G86" s="3">
         <v>203</v>
       </c>
-      <c r="H86" s="13" t="s">
+      <c r="H86" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I86" s="10">
@@ -3582,7 +4171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="87" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B87" s="7"/>
       <c r="C87" s="5">
         <v>7001</v>
@@ -3591,7 +4180,7 @@
         <v>20</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F87" s="5">
         <v>1</v>
@@ -3609,7 +4198,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="9"/>
     </row>
-    <row r="88" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="88" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B88" s="7"/>
       <c r="C88" s="5">
         <v>8001</v>
@@ -3618,7 +4207,7 @@
         <v>20</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F88" s="5">
         <v>1</v>
@@ -3636,7 +4225,7 @@
       <c r="K88" s="5"/>
       <c r="L88" s="9"/>
     </row>
-    <row r="89" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="89" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B89" s="7"/>
       <c r="C89" s="5">
         <v>9001</v>
@@ -3645,7 +4234,7 @@
         <v>55</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F89" s="5">
         <v>1</v>
@@ -3653,7 +4242,7 @@
       <c r="G89" s="5">
         <v>0</v>
       </c>
-      <c r="H89" s="13" t="s">
+      <c r="H89" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I89" s="5" t="s">
@@ -3663,11 +4252,11 @@
         <v>9</v>
       </c>
       <c r="K89" s="5"/>
-      <c r="L89" s="14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="90" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L89" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B90" s="7"/>
       <c r="C90" s="5">
         <v>10001</v>
@@ -3676,7 +4265,7 @@
         <v>55</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F90" s="5">
         <v>1</v>
@@ -3684,7 +4273,7 @@
       <c r="G90" s="5">
         <v>0</v>
       </c>
-      <c r="H90" s="13" t="s">
+      <c r="H90" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I90" s="5" t="s">
@@ -3694,11 +4283,11 @@
         <v>10</v>
       </c>
       <c r="K90" s="5"/>
-      <c r="L90" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="91" spans="2:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L90" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
       <c r="B91" s="7"/>
       <c r="C91" s="5">
         <v>11001</v>
@@ -3707,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F91" s="5">
         <v>1</v>
@@ -3715,7 +4304,7 @@
       <c r="G91" s="5">
         <v>0</v>
       </c>
-      <c r="H91" s="13" t="s">
+      <c r="H91" s="14" t="s">
         <v>45</v>
       </c>
       <c r="I91" s="5" t="s">
@@ -3725,14 +4314,151 @@
         <v>11</v>
       </c>
       <c r="K91" s="5"/>
-      <c r="L91" s="14" t="s">
-        <v>62</v>
-      </c>
+      <c r="L91" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="B92" s="7"/>
+      <c r="C92" s="5">
+        <v>12001</v>
+      </c>
+      <c r="D92" s="5">
+        <v>1</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F92" s="5">
+        <v>1</v>
+      </c>
+      <c r="G92" s="5">
+        <v>0</v>
+      </c>
+      <c r="H92" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" s="8">
+        <v>12</v>
+      </c>
+      <c r="K92" s="5"/>
+      <c r="L92" s="11"/>
+    </row>
+    <row r="93" s="1" customFormat="1" ht="24" customHeight="1" spans="2:12">
+      <c r="B93" s="7"/>
+      <c r="C93" s="5">
+        <v>12002</v>
+      </c>
+      <c r="D93" s="5">
+        <v>1</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F93" s="5">
+        <v>2</v>
+      </c>
+      <c r="G93" s="5">
+        <v>0</v>
+      </c>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J93" s="8">
+        <v>12</v>
+      </c>
+      <c r="K93" s="5"/>
+      <c r="L93" s="11"/>
+    </row>
+    <row r="94" s="1" customFormat="1" ht="24" customHeight="1" spans="2:12">
+      <c r="B94" s="7"/>
+      <c r="C94" s="5">
+        <v>12003</v>
+      </c>
+      <c r="D94" s="5">
+        <v>1</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F94" s="5">
+        <v>3</v>
+      </c>
+      <c r="G94" s="5">
+        <v>0</v>
+      </c>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J94" s="8">
+        <v>12</v>
+      </c>
+      <c r="K94" s="5"/>
+      <c r="L94" s="11"/>
+    </row>
+    <row r="95" s="1" customFormat="1" ht="24" customHeight="1" spans="2:12">
+      <c r="B95" s="7"/>
+      <c r="C95" s="5">
+        <v>12004</v>
+      </c>
+      <c r="D95" s="5">
+        <v>1</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F95" s="5">
+        <v>4</v>
+      </c>
+      <c r="G95" s="5">
+        <v>0</v>
+      </c>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" s="8">
+        <v>12</v>
+      </c>
+      <c r="K95" s="5"/>
+      <c r="L95" s="11"/>
+    </row>
+    <row r="96" s="1" customFormat="1" ht="24" customHeight="1" spans="2:12">
+      <c r="B96" s="7"/>
+      <c r="C96" s="5">
+        <v>12005</v>
+      </c>
+      <c r="D96" s="5">
+        <v>1</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F96" s="5">
+        <v>5</v>
+      </c>
+      <c r="G96" s="5">
+        <v>0</v>
+      </c>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J96" s="8">
+        <v>12</v>
+      </c>
+      <c r="K96" s="5"/>
+      <c r="L96" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/RobotConfig.xlsx
+++ b/Excel/RobotConfig.xlsx
@@ -135,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="67">
   <si>
     <t>cs</t>
   </si>
@@ -348,7 +348,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,13 +358,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -896,185 +889,185 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1398,7 +1391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -4455,6 +4448,143 @@
       <c r="K96" s="5"/>
       <c r="L96" s="11"/>
     </row>
+    <row r="97" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
+      <c r="B97" s="7"/>
+      <c r="C97" s="5">
+        <v>12006</v>
+      </c>
+      <c r="D97" s="5">
+        <v>1</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F97" s="5">
+        <v>1</v>
+      </c>
+      <c r="G97" s="5">
+        <v>0</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J97" s="8">
+        <v>12</v>
+      </c>
+      <c r="K97" s="5"/>
+      <c r="L97" s="11"/>
+    </row>
+    <row r="98" s="1" customFormat="1" ht="24" customHeight="1" spans="2:12">
+      <c r="B98" s="7"/>
+      <c r="C98" s="5">
+        <v>12007</v>
+      </c>
+      <c r="D98" s="5">
+        <v>1</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F98" s="5">
+        <v>2</v>
+      </c>
+      <c r="G98" s="5">
+        <v>0</v>
+      </c>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J98" s="8">
+        <v>12</v>
+      </c>
+      <c r="K98" s="5"/>
+      <c r="L98" s="11"/>
+    </row>
+    <row r="99" s="1" customFormat="1" ht="24" customHeight="1" spans="2:12">
+      <c r="B99" s="7"/>
+      <c r="C99" s="5">
+        <v>12008</v>
+      </c>
+      <c r="D99" s="5">
+        <v>1</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F99" s="5">
+        <v>3</v>
+      </c>
+      <c r="G99" s="5">
+        <v>0</v>
+      </c>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J99" s="8">
+        <v>12</v>
+      </c>
+      <c r="K99" s="5"/>
+      <c r="L99" s="11"/>
+    </row>
+    <row r="100" s="1" customFormat="1" ht="24" customHeight="1" spans="2:12">
+      <c r="B100" s="7"/>
+      <c r="C100" s="5">
+        <v>12009</v>
+      </c>
+      <c r="D100" s="5">
+        <v>1</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F100" s="5">
+        <v>4</v>
+      </c>
+      <c r="G100" s="5">
+        <v>0</v>
+      </c>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J100" s="8">
+        <v>12</v>
+      </c>
+      <c r="K100" s="5"/>
+      <c r="L100" s="11"/>
+    </row>
+    <row r="101" s="1" customFormat="1" ht="24" customHeight="1" spans="2:12">
+      <c r="B101" s="7"/>
+      <c r="C101" s="5">
+        <v>12010</v>
+      </c>
+      <c r="D101" s="5">
+        <v>1</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F101" s="5">
+        <v>5</v>
+      </c>
+      <c r="G101" s="5">
+        <v>0</v>
+      </c>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J101" s="8">
+        <v>12</v>
+      </c>
+      <c r="K101" s="5"/>
+      <c r="L101" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
